--- a/converted_files/834/834-all-files.xlsx
+++ b/converted_files/834/834-all-files.xlsx
@@ -59,7 +59,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:PD20"/>
+  <dimension ref="A1:PO20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -220,1945 +220,2000 @@
       </c>
       <c r="AF1" s="3" t="inlineStr">
         <is>
+          <t>MedicarePlanCode</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>MedicareEligibilityReasonCode</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
           <t>CobraEventCode</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>EmploymentStatusCode</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>StudentStatusCode</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>HandicapIndicator</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>DeathDate</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
         <is>
           <t>ConfidentialityCode</t>
         </is>
       </c>
-      <c r="AK1" s="3" t="inlineStr">
+      <c r="AN1" s="3" t="inlineStr">
         <is>
           <t>BirthSequenceNumber</t>
         </is>
       </c>
-      <c r="AL1" s="3" t="inlineStr">
+      <c r="AO1" s="3" t="inlineStr">
         <is>
           <t>Identifier</t>
         </is>
       </c>
-      <c r="AM1" s="3" t="inlineStr">
+      <c r="AP1" s="3" t="inlineStr">
         <is>
           <t>GroupOrPolicyNumber</t>
         </is>
       </c>
-      <c r="AN1" s="3" t="inlineStr">
+      <c r="AQ1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier1QualifierCode</t>
         </is>
       </c>
-      <c r="AO1" s="3" t="inlineStr">
+      <c r="AR1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier1Identification</t>
         </is>
       </c>
-      <c r="AP1" s="3" t="inlineStr">
+      <c r="AS1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier2QualifierCode</t>
         </is>
       </c>
-      <c r="AQ1" s="3" t="inlineStr">
+      <c r="AT1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier2Identification</t>
         </is>
       </c>
-      <c r="AR1" s="3" t="inlineStr">
+      <c r="AU1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier3QualifierCode</t>
         </is>
       </c>
-      <c r="AS1" s="3" t="inlineStr">
+      <c r="AV1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier3Identification</t>
         </is>
       </c>
-      <c r="AT1" s="3" t="inlineStr">
+      <c r="AW1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier4QualifierCode</t>
         </is>
       </c>
-      <c r="AU1" s="3" t="inlineStr">
+      <c r="AX1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier4Identification</t>
         </is>
       </c>
-      <c r="AV1" s="3" t="inlineStr">
+      <c r="AY1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier5QualifierCode</t>
         </is>
       </c>
-      <c r="AW1" s="3" t="inlineStr">
+      <c r="AZ1" s="3" t="inlineStr">
         <is>
           <t>SupplementalIdentifier5Identification</t>
         </is>
       </c>
-      <c r="AX1" s="3" t="inlineStr">
+      <c r="BA1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate1QualifierCode</t>
         </is>
       </c>
-      <c r="AY1" s="3" t="inlineStr">
+      <c r="BB1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate1Date</t>
         </is>
       </c>
-      <c r="AZ1" s="3" t="inlineStr">
+      <c r="BC1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate2QualifierCode</t>
         </is>
       </c>
-      <c r="BA1" s="3" t="inlineStr">
+      <c r="BD1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate2Date</t>
         </is>
       </c>
-      <c r="BB1" s="3" t="inlineStr">
+      <c r="BE1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate3QualifierCode</t>
         </is>
       </c>
-      <c r="BC1" s="3" t="inlineStr">
+      <c r="BF1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate3Date</t>
         </is>
       </c>
-      <c r="BD1" s="3" t="inlineStr">
+      <c r="BG1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate4QualifierCode</t>
         </is>
       </c>
-      <c r="BE1" s="3" t="inlineStr">
+      <c r="BH1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate4Date</t>
         </is>
       </c>
-      <c r="BF1" s="3" t="inlineStr">
+      <c r="BI1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate5QualifierCode</t>
         </is>
       </c>
-      <c r="BG1" s="3" t="inlineStr">
+      <c r="BJ1" s="3" t="inlineStr">
         <is>
           <t>StatusInfoEffectiveDate5Date</t>
         </is>
       </c>
-      <c r="BH1" s="3" t="inlineStr">
+      <c r="BK1" s="3" t="inlineStr">
         <is>
           <t>MemberEntityRole</t>
         </is>
       </c>
-      <c r="BI1" s="3" t="inlineStr">
+      <c r="BL1" s="3" t="inlineStr">
         <is>
           <t>MemberIdentificationType</t>
         </is>
       </c>
-      <c r="BJ1" s="3" t="inlineStr">
+      <c r="BM1" s="3" t="inlineStr">
         <is>
           <t>MemberIdentifier</t>
         </is>
       </c>
-      <c r="BK1" s="3" t="inlineStr">
+      <c r="BN1" s="3" t="inlineStr">
         <is>
           <t>MemberTaxId</t>
         </is>
       </c>
-      <c r="BL1" s="3" t="inlineStr">
+      <c r="BO1" s="3" t="inlineStr">
         <is>
           <t>MemberLastName</t>
         </is>
       </c>
-      <c r="BM1" s="3" t="inlineStr">
+      <c r="BP1" s="3" t="inlineStr">
         <is>
           <t>MemberFirstName</t>
         </is>
       </c>
-      <c r="BN1" s="3" t="inlineStr">
+      <c r="BQ1" s="3" t="inlineStr">
         <is>
           <t>MemberMiddleName</t>
         </is>
       </c>
-      <c r="BO1" s="3" t="inlineStr">
+      <c r="BR1" s="3" t="inlineStr">
         <is>
           <t>MemberBirthDate</t>
         </is>
       </c>
-      <c r="BP1" s="3" t="inlineStr">
+      <c r="BS1" s="3" t="inlineStr">
         <is>
           <t>MemberGender</t>
         </is>
       </c>
-      <c r="BQ1" s="3" t="inlineStr">
+      <c r="BT1" s="3" t="inlineStr">
         <is>
           <t>MemberAddressLine</t>
         </is>
       </c>
-      <c r="BR1" s="3" t="inlineStr">
+      <c r="BU1" s="3" t="inlineStr">
         <is>
           <t>MemberAddressLine2</t>
         </is>
       </c>
-      <c r="BS1" s="3" t="inlineStr">
+      <c r="BV1" s="3" t="inlineStr">
         <is>
           <t>MemberAddressCity</t>
         </is>
       </c>
-      <c r="BT1" s="3" t="inlineStr">
+      <c r="BW1" s="3" t="inlineStr">
         <is>
           <t>MemberAddressStateCode</t>
         </is>
       </c>
-      <c r="BU1" s="3" t="inlineStr">
+      <c r="BX1" s="3" t="inlineStr">
         <is>
           <t>MemberAddressZipCode</t>
         </is>
       </c>
-      <c r="BV1" s="3" t="inlineStr">
+      <c r="BY1" s="3" t="inlineStr">
         <is>
           <t>MemberContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="BW1" s="3" t="inlineStr">
+      <c r="BZ1" s="3" t="inlineStr">
         <is>
           <t>MemberContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="BX1" s="3" t="inlineStr">
+      <c r="CA1" s="3" t="inlineStr">
         <is>
           <t>MemberContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="BY1" s="3" t="inlineStr">
+      <c r="CB1" s="3" t="inlineStr">
         <is>
           <t>MemberContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="BZ1" s="3" t="inlineStr">
+      <c r="CC1" s="3" t="inlineStr">
         <is>
           <t>MemberMaritalStatusCode</t>
         </is>
       </c>
-      <c r="CA1" s="3" t="inlineStr">
-        <is>
-          <t>MemberEthnicityCode</t>
-        </is>
-      </c>
-      <c r="CB1" s="3" t="inlineStr">
+      <c r="CD1" s="3" t="inlineStr">
+        <is>
+          <t>MemberEthnicityCode1</t>
+        </is>
+      </c>
+      <c r="CE1" s="3" t="inlineStr">
+        <is>
+          <t>MemberEthnicityCode2</t>
+        </is>
+      </c>
+      <c r="CF1" s="3" t="inlineStr">
+        <is>
+          <t>MemberEthnicityCode3</t>
+        </is>
+      </c>
+      <c r="CG1" s="3" t="inlineStr">
         <is>
           <t>MemberCitizenshipCode</t>
         </is>
       </c>
-      <c r="CC1" s="3" t="inlineStr">
+      <c r="CH1" s="3" t="inlineStr">
         <is>
           <t>MemberEmploymentClassCode1</t>
         </is>
       </c>
-      <c r="CD1" s="3" t="inlineStr">
+      <c r="CI1" s="3" t="inlineStr">
         <is>
           <t>MemberEmploymentClassCode2</t>
         </is>
       </c>
-      <c r="CE1" s="3" t="inlineStr">
+      <c r="CJ1" s="3" t="inlineStr">
         <is>
           <t>MemberEmploymentClassCode3</t>
         </is>
       </c>
-      <c r="CF1" s="3" t="inlineStr">
+      <c r="CK1" s="3" t="inlineStr">
         <is>
           <t>MemberEmploymentClassCode4</t>
         </is>
       </c>
-      <c r="CG1" s="3" t="inlineStr">
+      <c r="CL1" s="3" t="inlineStr">
         <is>
           <t>MemberEmploymentClassCode5</t>
         </is>
       </c>
-      <c r="CH1" s="3" t="inlineStr">
+      <c r="CM1" s="3" t="inlineStr">
         <is>
           <t>MemberWageFrequencyCode</t>
         </is>
       </c>
-      <c r="CI1" s="3" t="inlineStr">
+      <c r="CN1" s="3" t="inlineStr">
         <is>
           <t>MemberWageAmount</t>
         </is>
       </c>
-      <c r="CJ1" s="3" t="inlineStr">
+      <c r="CO1" s="3" t="inlineStr">
         <is>
           <t>MemberWorkHoursCount</t>
         </is>
       </c>
-      <c r="CK1" s="3" t="inlineStr">
+      <c r="CP1" s="3" t="inlineStr">
         <is>
           <t>MemberEmployerLocationIdentificationCode</t>
         </is>
       </c>
-      <c r="CL1" s="3" t="inlineStr">
+      <c r="CQ1" s="3" t="inlineStr">
         <is>
           <t>MemberSalaryGradeCode</t>
         </is>
       </c>
-      <c r="CM1" s="3" t="inlineStr">
+      <c r="CR1" s="3" t="inlineStr">
         <is>
           <t>MemberHealthRelatedCode</t>
         </is>
       </c>
-      <c r="CN1" s="3" t="inlineStr">
+      <c r="CS1" s="3" t="inlineStr">
         <is>
           <t>MemberHeight</t>
         </is>
       </c>
-      <c r="CO1" s="3" t="inlineStr">
+      <c r="CT1" s="3" t="inlineStr">
         <is>
           <t>MemberWeight</t>
         </is>
       </c>
-      <c r="CP1" s="3" t="inlineStr">
+      <c r="CU1" s="3" t="inlineStr">
         <is>
           <t>MemberLanguageInfoCodeQualifier</t>
         </is>
       </c>
-      <c r="CQ1" s="3" t="inlineStr">
+      <c r="CV1" s="3" t="inlineStr">
         <is>
           <t>MemberLanguageInfoCode</t>
         </is>
       </c>
-      <c r="CR1" s="3" t="inlineStr">
+      <c r="CW1" s="3" t="inlineStr">
         <is>
           <t>MemberLanguageInfoLanguageDescription</t>
         </is>
       </c>
-      <c r="CS1" s="3" t="inlineStr">
+      <c r="CX1" s="3" t="inlineStr">
         <is>
           <t>MemberLanguageInfoLanguageUseIndicator</t>
         </is>
       </c>
-      <c r="CT1" s="3" t="inlineStr">
+      <c r="CY1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberIdentifier</t>
         </is>
       </c>
-      <c r="CU1" s="3" t="inlineStr">
+      <c r="CZ1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberLastName</t>
         </is>
       </c>
-      <c r="CV1" s="3" t="inlineStr">
+      <c r="DA1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberFirstName</t>
         </is>
       </c>
-      <c r="CW1" s="3" t="inlineStr">
+      <c r="DB1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberMiddleName</t>
         </is>
       </c>
-      <c r="CX1" s="3" t="inlineStr">
+      <c r="DC1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberBirthDate</t>
         </is>
       </c>
-      <c r="CY1" s="3" t="inlineStr">
+      <c r="DD1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberGender</t>
         </is>
       </c>
-      <c r="CZ1" s="3" t="inlineStr">
+      <c r="DE1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberMaritalStatusCode</t>
         </is>
       </c>
-      <c r="DA1" s="3" t="inlineStr">
+      <c r="DF1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberEthnicityCode</t>
         </is>
       </c>
-      <c r="DB1" s="3" t="inlineStr">
+      <c r="DG1" s="3" t="inlineStr">
         <is>
           <t>IncorrectMemberCitizenshipCode</t>
         </is>
       </c>
-      <c r="DC1" s="3" t="inlineStr">
+      <c r="DH1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount1QualifierCode</t>
         </is>
       </c>
-      <c r="DD1" s="3" t="inlineStr">
+      <c r="DI1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount1Amount</t>
         </is>
       </c>
-      <c r="DE1" s="3" t="inlineStr">
+      <c r="DJ1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount2QualifierCode</t>
         </is>
       </c>
-      <c r="DF1" s="3" t="inlineStr">
+      <c r="DK1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount2Amount</t>
         </is>
       </c>
-      <c r="DG1" s="3" t="inlineStr">
+      <c r="DL1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount3QualifierCode</t>
         </is>
       </c>
-      <c r="DH1" s="3" t="inlineStr">
+      <c r="DM1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount3Amount</t>
         </is>
       </c>
-      <c r="DI1" s="3" t="inlineStr">
+      <c r="DN1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount4QualifierCode</t>
         </is>
       </c>
-      <c r="DJ1" s="3" t="inlineStr">
+      <c r="DO1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount4Amount</t>
         </is>
       </c>
-      <c r="DK1" s="3" t="inlineStr">
+      <c r="DP1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount5QualifierCode</t>
         </is>
       </c>
-      <c r="DL1" s="3" t="inlineStr">
+      <c r="DQ1" s="3" t="inlineStr">
         <is>
           <t>ContractAmount5Amount</t>
         </is>
       </c>
-      <c r="DM1" s="3" t="inlineStr">
+      <c r="DR1" s="3" t="inlineStr">
         <is>
           <t>MailingAddressLine</t>
         </is>
       </c>
-      <c r="DN1" s="3" t="inlineStr">
+      <c r="DS1" s="3" t="inlineStr">
         <is>
           <t>MailingAddressLine2</t>
         </is>
       </c>
-      <c r="DO1" s="3" t="inlineStr">
+      <c r="DT1" s="3" t="inlineStr">
         <is>
           <t>MailingAddressCity</t>
         </is>
       </c>
-      <c r="DP1" s="3" t="inlineStr">
+      <c r="DU1" s="3" t="inlineStr">
         <is>
           <t>MailingAddressStateCode</t>
         </is>
       </c>
-      <c r="DQ1" s="3" t="inlineStr">
+      <c r="DV1" s="3" t="inlineStr">
         <is>
           <t>MailingAddressZipCode</t>
         </is>
       </c>
-      <c r="DR1" s="3" t="inlineStr">
+      <c r="DW1" s="3" t="inlineStr">
         <is>
           <t>Employer1Identifier</t>
         </is>
       </c>
-      <c r="DS1" s="3" t="inlineStr">
+      <c r="DX1" s="3" t="inlineStr">
         <is>
           <t>Employer1LastNameOrOrgName</t>
         </is>
       </c>
-      <c r="DT1" s="3" t="inlineStr">
+      <c r="DY1" s="3" t="inlineStr">
         <is>
           <t>Employer1FirstName</t>
         </is>
       </c>
-      <c r="DU1" s="3" t="inlineStr">
+      <c r="DZ1" s="3" t="inlineStr">
         <is>
           <t>Employer1MiddleName</t>
         </is>
       </c>
-      <c r="DV1" s="3" t="inlineStr">
+      <c r="EA1" s="3" t="inlineStr">
         <is>
           <t>Employer1AddressLine</t>
         </is>
       </c>
-      <c r="DW1" s="3" t="inlineStr">
+      <c r="EB1" s="3" t="inlineStr">
         <is>
           <t>Employer1AddressLine2</t>
         </is>
       </c>
-      <c r="DX1" s="3" t="inlineStr">
+      <c r="EC1" s="3" t="inlineStr">
         <is>
           <t>Employer1AddressCity</t>
         </is>
       </c>
-      <c r="DY1" s="3" t="inlineStr">
+      <c r="ED1" s="3" t="inlineStr">
         <is>
           <t>Employer1AddressStateCode</t>
         </is>
       </c>
-      <c r="DZ1" s="3" t="inlineStr">
+      <c r="EE1" s="3" t="inlineStr">
         <is>
           <t>Employer1AddressZipCode</t>
         </is>
       </c>
-      <c r="EA1" s="3" t="inlineStr">
+      <c r="EF1" s="3" t="inlineStr">
         <is>
           <t>Employer1ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="EB1" s="3" t="inlineStr">
+      <c r="EG1" s="3" t="inlineStr">
         <is>
           <t>Employer1ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="EC1" s="3" t="inlineStr">
+      <c r="EH1" s="3" t="inlineStr">
         <is>
           <t>Employer1ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="ED1" s="3" t="inlineStr">
+      <c r="EI1" s="3" t="inlineStr">
         <is>
           <t>Employer1ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="EE1" s="3" t="inlineStr">
+      <c r="EJ1" s="3" t="inlineStr">
         <is>
           <t>Employer2Identifier</t>
         </is>
       </c>
-      <c r="EF1" s="3" t="inlineStr">
+      <c r="EK1" s="3" t="inlineStr">
         <is>
           <t>Employer2LastNameOrOrgName</t>
         </is>
       </c>
-      <c r="EG1" s="3" t="inlineStr">
+      <c r="EL1" s="3" t="inlineStr">
         <is>
           <t>Employer2FirstName</t>
         </is>
       </c>
-      <c r="EH1" s="3" t="inlineStr">
+      <c r="EM1" s="3" t="inlineStr">
         <is>
           <t>Employer2MiddleName</t>
         </is>
       </c>
-      <c r="EI1" s="3" t="inlineStr">
+      <c r="EN1" s="3" t="inlineStr">
         <is>
           <t>Employer2AddressLine</t>
         </is>
       </c>
-      <c r="EJ1" s="3" t="inlineStr">
+      <c r="EO1" s="3" t="inlineStr">
         <is>
           <t>Employer2AddressLine2</t>
         </is>
       </c>
-      <c r="EK1" s="3" t="inlineStr">
+      <c r="EP1" s="3" t="inlineStr">
         <is>
           <t>Employer2AddressCity</t>
         </is>
       </c>
-      <c r="EL1" s="3" t="inlineStr">
+      <c r="EQ1" s="3" t="inlineStr">
         <is>
           <t>Employer2AddressStateCode</t>
         </is>
       </c>
-      <c r="EM1" s="3" t="inlineStr">
+      <c r="ER1" s="3" t="inlineStr">
         <is>
           <t>Employer2AddressZipCode</t>
         </is>
       </c>
-      <c r="EN1" s="3" t="inlineStr">
+      <c r="ES1" s="3" t="inlineStr">
         <is>
           <t>Employer2ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="EO1" s="3" t="inlineStr">
+      <c r="ET1" s="3" t="inlineStr">
         <is>
           <t>Employer2ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="EP1" s="3" t="inlineStr">
+      <c r="EU1" s="3" t="inlineStr">
         <is>
           <t>Employer2ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="EQ1" s="3" t="inlineStr">
+      <c r="EV1" s="3" t="inlineStr">
         <is>
           <t>Employer2ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="ER1" s="3" t="inlineStr">
+      <c r="EW1" s="3" t="inlineStr">
         <is>
           <t>School1Identifier</t>
         </is>
       </c>
-      <c r="ES1" s="3" t="inlineStr">
+      <c r="EX1" s="3" t="inlineStr">
         <is>
           <t>School1Name</t>
         </is>
       </c>
-      <c r="ET1" s="3" t="inlineStr">
+      <c r="EY1" s="3" t="inlineStr">
         <is>
           <t>School1AddressLine</t>
         </is>
       </c>
-      <c r="EU1" s="3" t="inlineStr">
+      <c r="EZ1" s="3" t="inlineStr">
         <is>
           <t>School1AddressLine2</t>
         </is>
       </c>
-      <c r="EV1" s="3" t="inlineStr">
+      <c r="FA1" s="3" t="inlineStr">
         <is>
           <t>School1AddressCity</t>
         </is>
       </c>
-      <c r="EW1" s="3" t="inlineStr">
+      <c r="FB1" s="3" t="inlineStr">
         <is>
           <t>School1AddressStateCode</t>
         </is>
       </c>
-      <c r="EX1" s="3" t="inlineStr">
+      <c r="FC1" s="3" t="inlineStr">
         <is>
           <t>School1AddressZipCode</t>
         </is>
       </c>
-      <c r="EY1" s="3" t="inlineStr">
+      <c r="FD1" s="3" t="inlineStr">
         <is>
           <t>School1ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="EZ1" s="3" t="inlineStr">
+      <c r="FE1" s="3" t="inlineStr">
         <is>
           <t>School1ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="FA1" s="3" t="inlineStr">
+      <c r="FF1" s="3" t="inlineStr">
         <is>
           <t>School1ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="FB1" s="3" t="inlineStr">
+      <c r="FG1" s="3" t="inlineStr">
         <is>
           <t>School1ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="FC1" s="3" t="inlineStr">
+      <c r="FH1" s="3" t="inlineStr">
         <is>
           <t>School2Identifier</t>
         </is>
       </c>
-      <c r="FD1" s="3" t="inlineStr">
+      <c r="FI1" s="3" t="inlineStr">
         <is>
           <t>School2Name</t>
         </is>
       </c>
-      <c r="FE1" s="3" t="inlineStr">
+      <c r="FJ1" s="3" t="inlineStr">
         <is>
           <t>School2AddressLine</t>
         </is>
       </c>
-      <c r="FF1" s="3" t="inlineStr">
+      <c r="FK1" s="3" t="inlineStr">
         <is>
           <t>School2AddressLine2</t>
         </is>
       </c>
-      <c r="FG1" s="3" t="inlineStr">
+      <c r="FL1" s="3" t="inlineStr">
         <is>
           <t>School2AddressCity</t>
         </is>
       </c>
-      <c r="FH1" s="3" t="inlineStr">
+      <c r="FM1" s="3" t="inlineStr">
         <is>
           <t>School2AddressStateCode</t>
         </is>
       </c>
-      <c r="FI1" s="3" t="inlineStr">
+      <c r="FN1" s="3" t="inlineStr">
         <is>
           <t>School2AddressZipCode</t>
         </is>
       </c>
-      <c r="FJ1" s="3" t="inlineStr">
+      <c r="FO1" s="3" t="inlineStr">
         <is>
           <t>School2ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="FK1" s="3" t="inlineStr">
+      <c r="FP1" s="3" t="inlineStr">
         <is>
           <t>School2ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="FL1" s="3" t="inlineStr">
+      <c r="FQ1" s="3" t="inlineStr">
         <is>
           <t>School2ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="FM1" s="3" t="inlineStr">
+      <c r="FR1" s="3" t="inlineStr">
         <is>
           <t>School2ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="FN1" s="3" t="inlineStr">
+      <c r="FS1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentIdentifier</t>
         </is>
       </c>
-      <c r="FO1" s="3" t="inlineStr">
+      <c r="FT1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentLastName</t>
         </is>
       </c>
-      <c r="FP1" s="3" t="inlineStr">
+      <c r="FU1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentFirstName</t>
         </is>
       </c>
-      <c r="FQ1" s="3" t="inlineStr">
+      <c r="FV1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentMiddleName</t>
         </is>
       </c>
-      <c r="FR1" s="3" t="inlineStr">
+      <c r="FW1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentAddressLine</t>
         </is>
       </c>
-      <c r="FS1" s="3" t="inlineStr">
+      <c r="FX1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentAddressLine2</t>
         </is>
       </c>
-      <c r="FT1" s="3" t="inlineStr">
+      <c r="FY1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentAddressCity</t>
         </is>
       </c>
-      <c r="FU1" s="3" t="inlineStr">
+      <c r="FZ1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentAddressStateCode</t>
         </is>
       </c>
-      <c r="FV1" s="3" t="inlineStr">
+      <c r="GA1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentAddressZipCode</t>
         </is>
       </c>
-      <c r="FW1" s="3" t="inlineStr">
+      <c r="GB1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="FX1" s="3" t="inlineStr">
+      <c r="GC1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="FY1" s="3" t="inlineStr">
+      <c r="GD1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="FZ1" s="3" t="inlineStr">
+      <c r="GE1" s="3" t="inlineStr">
         <is>
           <t>CustodialParentContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="GA1" s="3" t="inlineStr">
+      <c r="GF1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1EntityRole</t>
         </is>
       </c>
-      <c r="GB1" s="3" t="inlineStr">
+      <c r="GG1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1Identifier</t>
         </is>
       </c>
-      <c r="GC1" s="3" t="inlineStr">
+      <c r="GH1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1LastName</t>
         </is>
       </c>
-      <c r="GD1" s="3" t="inlineStr">
+      <c r="GI1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1FirstName</t>
         </is>
       </c>
-      <c r="GE1" s="3" t="inlineStr">
+      <c r="GJ1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1MiddleName</t>
         </is>
       </c>
-      <c r="GF1" s="3" t="inlineStr">
+      <c r="GK1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1AddressLine</t>
         </is>
       </c>
-      <c r="GG1" s="3" t="inlineStr">
+      <c r="GL1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1AddressLine2</t>
         </is>
       </c>
-      <c r="GH1" s="3" t="inlineStr">
+      <c r="GM1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1AddressCity</t>
         </is>
       </c>
-      <c r="GI1" s="3" t="inlineStr">
+      <c r="GN1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1AddressStateCode</t>
         </is>
       </c>
-      <c r="GJ1" s="3" t="inlineStr">
+      <c r="GO1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1AddressZipCode</t>
         </is>
       </c>
-      <c r="GK1" s="3" t="inlineStr">
+      <c r="GP1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="GL1" s="3" t="inlineStr">
+      <c r="GQ1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="GM1" s="3" t="inlineStr">
+      <c r="GR1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="GN1" s="3" t="inlineStr">
+      <c r="GS1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson1ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="GO1" s="3" t="inlineStr">
+      <c r="GT1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2EntityRole</t>
         </is>
       </c>
-      <c r="GP1" s="3" t="inlineStr">
+      <c r="GU1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2Identifier</t>
         </is>
       </c>
-      <c r="GQ1" s="3" t="inlineStr">
+      <c r="GV1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2LastName</t>
         </is>
       </c>
-      <c r="GR1" s="3" t="inlineStr">
+      <c r="GW1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2FirstName</t>
         </is>
       </c>
-      <c r="GS1" s="3" t="inlineStr">
+      <c r="GX1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2MiddleName</t>
         </is>
       </c>
-      <c r="GT1" s="3" t="inlineStr">
+      <c r="GY1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2AddressLine</t>
         </is>
       </c>
-      <c r="GU1" s="3" t="inlineStr">
+      <c r="GZ1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2AddressLine2</t>
         </is>
       </c>
-      <c r="GV1" s="3" t="inlineStr">
+      <c r="HA1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2AddressCity</t>
         </is>
       </c>
-      <c r="GW1" s="3" t="inlineStr">
+      <c r="HB1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2AddressStateCode</t>
         </is>
       </c>
-      <c r="GX1" s="3" t="inlineStr">
+      <c r="HC1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2AddressZipCode</t>
         </is>
       </c>
-      <c r="GY1" s="3" t="inlineStr">
+      <c r="HD1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="GZ1" s="3" t="inlineStr">
+      <c r="HE1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="HA1" s="3" t="inlineStr">
+      <c r="HF1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="HB1" s="3" t="inlineStr">
+      <c r="HG1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson2ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="HC1" s="3" t="inlineStr">
+      <c r="HH1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3EntityRole</t>
         </is>
       </c>
-      <c r="HD1" s="3" t="inlineStr">
+      <c r="HI1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3Identifier</t>
         </is>
       </c>
-      <c r="HE1" s="3" t="inlineStr">
+      <c r="HJ1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3LastName</t>
         </is>
       </c>
-      <c r="HF1" s="3" t="inlineStr">
+      <c r="HK1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3FirstName</t>
         </is>
       </c>
-      <c r="HG1" s="3" t="inlineStr">
+      <c r="HL1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3MiddleName</t>
         </is>
       </c>
-      <c r="HH1" s="3" t="inlineStr">
+      <c r="HM1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3AddressLine</t>
         </is>
       </c>
-      <c r="HI1" s="3" t="inlineStr">
+      <c r="HN1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3AddressLine2</t>
         </is>
       </c>
-      <c r="HJ1" s="3" t="inlineStr">
+      <c r="HO1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3AddressCity</t>
         </is>
       </c>
-      <c r="HK1" s="3" t="inlineStr">
+      <c r="HP1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3AddressStateCode</t>
         </is>
       </c>
-      <c r="HL1" s="3" t="inlineStr">
+      <c r="HQ1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3AddressZipCode</t>
         </is>
       </c>
-      <c r="HM1" s="3" t="inlineStr">
+      <c r="HR1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="HN1" s="3" t="inlineStr">
+      <c r="HS1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="HO1" s="3" t="inlineStr">
+      <c r="HT1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="HP1" s="3" t="inlineStr">
+      <c r="HU1" s="3" t="inlineStr">
         <is>
           <t>ResponsiblePerson3ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="HQ1" s="3" t="inlineStr">
+      <c r="HV1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="HR1" s="3" t="inlineStr">
+      <c r="HW1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationFirstName</t>
         </is>
       </c>
-      <c r="HS1" s="3" t="inlineStr">
+      <c r="HX1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationMiddleName</t>
         </is>
       </c>
-      <c r="HT1" s="3" t="inlineStr">
+      <c r="HY1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationAddressLine</t>
         </is>
       </c>
-      <c r="HU1" s="3" t="inlineStr">
+      <c r="HZ1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationAddressLine2</t>
         </is>
       </c>
-      <c r="HV1" s="3" t="inlineStr">
+      <c r="IA1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationAddressCity</t>
         </is>
       </c>
-      <c r="HW1" s="3" t="inlineStr">
+      <c r="IB1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationAddressStateCode</t>
         </is>
       </c>
-      <c r="HX1" s="3" t="inlineStr">
+      <c r="IC1" s="3" t="inlineStr">
         <is>
           <t>DropOffLocationAddressZipCode</t>
         </is>
       </c>
-      <c r="HY1" s="3" t="inlineStr">
+      <c r="ID1" s="3" t="inlineStr">
         <is>
           <t>Disability1TypeCode</t>
         </is>
       </c>
-      <c r="HZ1" s="3" t="inlineStr">
+      <c r="IE1" s="3" t="inlineStr">
         <is>
           <t>Disability1DiagnosisCode</t>
         </is>
       </c>
-      <c r="IA1" s="3" t="inlineStr">
+      <c r="IF1" s="3" t="inlineStr">
         <is>
           <t>Disability1DateFrom</t>
         </is>
       </c>
-      <c r="IB1" s="3" t="inlineStr">
+      <c r="IG1" s="3" t="inlineStr">
         <is>
           <t>Disability1DateTo</t>
         </is>
       </c>
-      <c r="IC1" s="3" t="inlineStr">
+      <c r="IH1" s="3" t="inlineStr">
         <is>
           <t>Disability2TypeCode</t>
         </is>
       </c>
-      <c r="ID1" s="3" t="inlineStr">
+      <c r="II1" s="3" t="inlineStr">
         <is>
           <t>Disability2DiagnosisCode</t>
         </is>
       </c>
-      <c r="IE1" s="3" t="inlineStr">
+      <c r="IJ1" s="3" t="inlineStr">
         <is>
           <t>Disability2DateFrom</t>
         </is>
       </c>
-      <c r="IF1" s="3" t="inlineStr">
+      <c r="IK1" s="3" t="inlineStr">
         <is>
           <t>Disability2DateTo</t>
         </is>
       </c>
-      <c r="IG1" s="3" t="inlineStr">
+      <c r="IL1" s="3" t="inlineStr">
         <is>
           <t>Disability3TypeCode</t>
         </is>
       </c>
-      <c r="IH1" s="3" t="inlineStr">
+      <c r="IM1" s="3" t="inlineStr">
         <is>
           <t>Disability3DiagnosisCode</t>
         </is>
       </c>
-      <c r="II1" s="3" t="inlineStr">
+      <c r="IN1" s="3" t="inlineStr">
         <is>
           <t>Disability3DateFrom</t>
         </is>
       </c>
-      <c r="IJ1" s="3" t="inlineStr">
+      <c r="IO1" s="3" t="inlineStr">
         <is>
           <t>Disability3DateTo</t>
         </is>
       </c>
-      <c r="IK1" s="3" t="inlineStr">
+      <c r="IP1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory1Name</t>
         </is>
       </c>
-      <c r="IL1" s="3" t="inlineStr">
+      <c r="IQ1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory1IdentifierQualifierCode</t>
         </is>
       </c>
-      <c r="IM1" s="3" t="inlineStr">
+      <c r="IR1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory1IdentifierType</t>
         </is>
       </c>
-      <c r="IN1" s="3" t="inlineStr">
+      <c r="IS1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory1Identifier</t>
         </is>
       </c>
-      <c r="IO1" s="3" t="inlineStr">
+      <c r="IT1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory1Date</t>
         </is>
       </c>
-      <c r="IP1" s="3" t="inlineStr">
+      <c r="IU1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory1DateTo</t>
         </is>
       </c>
-      <c r="IQ1" s="3" t="inlineStr">
+      <c r="IV1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory2Name</t>
         </is>
       </c>
-      <c r="IR1" s="3" t="inlineStr">
+      <c r="IW1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory2IdentifierQualifierCode</t>
         </is>
       </c>
-      <c r="IS1" s="3" t="inlineStr">
+      <c r="IX1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory2IdentifierType</t>
         </is>
       </c>
-      <c r="IT1" s="3" t="inlineStr">
+      <c r="IY1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory2Identifier</t>
         </is>
       </c>
-      <c r="IU1" s="3" t="inlineStr">
+      <c r="IZ1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory2Date</t>
         </is>
       </c>
-      <c r="IV1" s="3" t="inlineStr">
+      <c r="JA1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory2DateTo</t>
         </is>
       </c>
-      <c r="IW1" s="3" t="inlineStr">
+      <c r="JB1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory3Name</t>
         </is>
       </c>
-      <c r="IX1" s="3" t="inlineStr">
+      <c r="JC1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory3IdentifierQualifierCode</t>
         </is>
       </c>
-      <c r="IY1" s="3" t="inlineStr">
+      <c r="JD1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory3IdentifierType</t>
         </is>
       </c>
-      <c r="IZ1" s="3" t="inlineStr">
+      <c r="JE1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory3Identifier</t>
         </is>
       </c>
-      <c r="JA1" s="3" t="inlineStr">
+      <c r="JF1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory3Date</t>
         </is>
       </c>
-      <c r="JB1" s="3" t="inlineStr">
+      <c r="JG1" s="3" t="inlineStr">
         <is>
           <t>ReportingCategory3DateTo</t>
         </is>
       </c>
-      <c r="JC1" s="3" t="inlineStr">
+      <c r="JH1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageMaintenanceTypeCode</t>
         </is>
       </c>
-      <c r="JD1" s="3" t="inlineStr">
+      <c r="JI1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageInsuranceLineCode</t>
         </is>
       </c>
-      <c r="JE1" s="3" t="inlineStr">
+      <c r="JJ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoveragePlanDescription</t>
         </is>
       </c>
-      <c r="JF1" s="3" t="inlineStr">
+      <c r="JK1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageLevelCode</t>
         </is>
       </c>
-      <c r="JG1" s="3" t="inlineStr">
+      <c r="JL1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageLateEnrollmentIndicator</t>
         </is>
       </c>
-      <c r="JH1" s="3" t="inlineStr">
+      <c r="JM1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate1QualifierCode</t>
         </is>
       </c>
-      <c r="JI1" s="3" t="inlineStr">
+      <c r="JN1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate1Date</t>
         </is>
       </c>
-      <c r="JJ1" s="3" t="inlineStr">
+      <c r="JO1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate2QualifierCode</t>
         </is>
       </c>
-      <c r="JK1" s="3" t="inlineStr">
+      <c r="JP1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate2Date</t>
         </is>
       </c>
-      <c r="JL1" s="3" t="inlineStr">
+      <c r="JQ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate3QualifierCode</t>
         </is>
       </c>
-      <c r="JM1" s="3" t="inlineStr">
+      <c r="JR1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate3Date</t>
         </is>
       </c>
-      <c r="JN1" s="3" t="inlineStr">
+      <c r="JS1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate4QualifierCode</t>
         </is>
       </c>
-      <c r="JO1" s="3" t="inlineStr">
+      <c r="JT1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate4Date</t>
         </is>
       </c>
-      <c r="JP1" s="3" t="inlineStr">
+      <c r="JU1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate5QualifierCode</t>
         </is>
       </c>
-      <c r="JQ1" s="3" t="inlineStr">
+      <c r="JV1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCoverageDate5Date</t>
         </is>
       </c>
-      <c r="JR1" s="3" t="inlineStr">
+      <c r="JW1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageContractAmount1QualifierCode</t>
         </is>
       </c>
-      <c r="JS1" s="3" t="inlineStr">
+      <c r="JX1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageContractAmount1Amount</t>
         </is>
       </c>
-      <c r="JT1" s="3" t="inlineStr">
+      <c r="JY1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageContractAmount2QualifierCode</t>
         </is>
       </c>
-      <c r="JU1" s="3" t="inlineStr">
+      <c r="JZ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageContractAmount2Amount</t>
         </is>
       </c>
-      <c r="JV1" s="3" t="inlineStr">
+      <c r="KA1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageContractAmount3QualifierCode</t>
         </is>
       </c>
-      <c r="JW1" s="3" t="inlineStr">
+      <c r="KB1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageContractAmount3Amount</t>
         </is>
       </c>
-      <c r="JX1" s="3" t="inlineStr">
+      <c r="KC1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber1QualifierCode</t>
         </is>
       </c>
-      <c r="JY1" s="3" t="inlineStr">
+      <c r="KD1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber1Identification</t>
         </is>
       </c>
-      <c r="JZ1" s="3" t="inlineStr">
+      <c r="KE1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber2QualifierCode</t>
         </is>
       </c>
-      <c r="KA1" s="3" t="inlineStr">
+      <c r="KF1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber2Identification</t>
         </is>
       </c>
-      <c r="KB1" s="3" t="inlineStr">
+      <c r="KG1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber3QualifierCode</t>
         </is>
       </c>
-      <c r="KC1" s="3" t="inlineStr">
+      <c r="KH1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber3Identification</t>
         </is>
       </c>
-      <c r="KD1" s="3" t="inlineStr">
+      <c r="KI1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber4QualifierCode</t>
         </is>
       </c>
-      <c r="KE1" s="3" t="inlineStr">
+      <c r="KJ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber4Identification</t>
         </is>
       </c>
-      <c r="KF1" s="3" t="inlineStr">
+      <c r="KK1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber5QualifierCode</t>
         </is>
       </c>
-      <c r="KG1" s="3" t="inlineStr">
+      <c r="KL1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageGroupOrPolicyNumber5Identification</t>
         </is>
       </c>
-      <c r="KH1" s="3" t="inlineStr">
+      <c r="KM1" s="3" t="inlineStr">
         <is>
           <t>HealthCoveragePriorCoverageMonthCount</t>
         </is>
       </c>
-      <c r="KI1" s="3" t="inlineStr">
+      <c r="KN1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageIdCardPlanDesc</t>
         </is>
       </c>
-      <c r="KJ1" s="3" t="inlineStr">
+      <c r="KO1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageIdCardTypeCode</t>
         </is>
       </c>
-      <c r="KK1" s="3" t="inlineStr">
+      <c r="KP1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageIdCardCount</t>
         </is>
       </c>
-      <c r="KL1" s="3" t="inlineStr">
+      <c r="KQ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageIdCardActionCode</t>
         </is>
       </c>
-      <c r="KM1" s="3" t="inlineStr">
+      <c r="KR1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1EntityRole</t>
         </is>
       </c>
-      <c r="KN1" s="3" t="inlineStr">
+      <c r="KS1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1EntityType</t>
         </is>
       </c>
-      <c r="KO1" s="3" t="inlineStr">
+      <c r="KT1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1Identifier</t>
         </is>
       </c>
-      <c r="KP1" s="3" t="inlineStr">
+      <c r="KU1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1LastNameOrOrgName</t>
         </is>
       </c>
-      <c r="KQ1" s="3" t="inlineStr">
+      <c r="KV1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1FirstName</t>
         </is>
       </c>
-      <c r="KR1" s="3" t="inlineStr">
+      <c r="KW1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1MiddleName</t>
         </is>
       </c>
-      <c r="KS1" s="3" t="inlineStr">
+      <c r="KX1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1AddressLine</t>
         </is>
       </c>
-      <c r="KT1" s="3" t="inlineStr">
+      <c r="KY1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1AddressLine2</t>
         </is>
       </c>
-      <c r="KU1" s="3" t="inlineStr">
+      <c r="KZ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1AddressCity</t>
         </is>
       </c>
-      <c r="KV1" s="3" t="inlineStr">
+      <c r="LA1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1AddressStateCode</t>
         </is>
       </c>
-      <c r="KW1" s="3" t="inlineStr">
+      <c r="LB1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1AddressZipCode</t>
         </is>
       </c>
-      <c r="KX1" s="3" t="inlineStr">
+      <c r="LC1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="KY1" s="3" t="inlineStr">
+      <c r="LD1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="KZ1" s="3" t="inlineStr">
+      <c r="LE1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="LA1" s="3" t="inlineStr">
+      <c r="LF1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="LB1" s="3" t="inlineStr">
+      <c r="LG1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1ChangeReasonActionCode</t>
         </is>
       </c>
-      <c r="LC1" s="3" t="inlineStr">
+      <c r="LH1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1ChangeReasonEffectiveDate</t>
         </is>
       </c>
-      <c r="LD1" s="3" t="inlineStr">
+      <c r="LI1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider1ChangeReasonReasonCode</t>
         </is>
       </c>
-      <c r="LE1" s="3" t="inlineStr">
+      <c r="LJ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2EntityRole</t>
         </is>
       </c>
-      <c r="LF1" s="3" t="inlineStr">
+      <c r="LK1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2EntityType</t>
         </is>
       </c>
-      <c r="LG1" s="3" t="inlineStr">
+      <c r="LL1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2Identifier</t>
         </is>
       </c>
-      <c r="LH1" s="3" t="inlineStr">
+      <c r="LM1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2LastNameOrOrgName</t>
         </is>
       </c>
-      <c r="LI1" s="3" t="inlineStr">
+      <c r="LN1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2FirstName</t>
         </is>
       </c>
-      <c r="LJ1" s="3" t="inlineStr">
+      <c r="LO1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2MiddleName</t>
         </is>
       </c>
-      <c r="LK1" s="3" t="inlineStr">
+      <c r="LP1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2AddressLine</t>
         </is>
       </c>
-      <c r="LL1" s="3" t="inlineStr">
+      <c r="LQ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2AddressLine2</t>
         </is>
       </c>
-      <c r="LM1" s="3" t="inlineStr">
+      <c r="LR1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2AddressCity</t>
         </is>
       </c>
-      <c r="LN1" s="3" t="inlineStr">
+      <c r="LS1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2AddressStateCode</t>
         </is>
       </c>
-      <c r="LO1" s="3" t="inlineStr">
+      <c r="LT1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2AddressZipCode</t>
         </is>
       </c>
-      <c r="LP1" s="3" t="inlineStr">
+      <c r="LU1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="LQ1" s="3" t="inlineStr">
+      <c r="LV1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="LR1" s="3" t="inlineStr">
+      <c r="LW1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="LS1" s="3" t="inlineStr">
+      <c r="LX1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="LT1" s="3" t="inlineStr">
+      <c r="LY1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2ChangeReasonActionCode</t>
         </is>
       </c>
-      <c r="LU1" s="3" t="inlineStr">
+      <c r="LZ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2ChangeReasonEffectiveDate</t>
         </is>
       </c>
-      <c r="LV1" s="3" t="inlineStr">
+      <c r="MA1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider2ChangeReasonReasonCode</t>
         </is>
       </c>
-      <c r="LW1" s="3" t="inlineStr">
+      <c r="MB1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3EntityRole</t>
         </is>
       </c>
-      <c r="LX1" s="3" t="inlineStr">
+      <c r="MC1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3EntityType</t>
         </is>
       </c>
-      <c r="LY1" s="3" t="inlineStr">
+      <c r="MD1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3Identifier</t>
         </is>
       </c>
-      <c r="LZ1" s="3" t="inlineStr">
+      <c r="ME1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3LastNameOrOrgName</t>
         </is>
       </c>
-      <c r="MA1" s="3" t="inlineStr">
+      <c r="MF1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3FirstName</t>
         </is>
       </c>
-      <c r="MB1" s="3" t="inlineStr">
+      <c r="MG1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3MiddleName</t>
         </is>
       </c>
-      <c r="MC1" s="3" t="inlineStr">
+      <c r="MH1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3AddressLine</t>
         </is>
       </c>
-      <c r="MD1" s="3" t="inlineStr">
+      <c r="MI1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3AddressLine2</t>
         </is>
       </c>
-      <c r="ME1" s="3" t="inlineStr">
+      <c r="MJ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3AddressCity</t>
         </is>
       </c>
-      <c r="MF1" s="3" t="inlineStr">
+      <c r="MK1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3AddressStateCode</t>
         </is>
       </c>
-      <c r="MG1" s="3" t="inlineStr">
+      <c r="ML1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3AddressZipCode</t>
         </is>
       </c>
-      <c r="MH1" s="3" t="inlineStr">
+      <c r="MM1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="MI1" s="3" t="inlineStr">
+      <c r="MN1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="MJ1" s="3" t="inlineStr">
+      <c r="MO1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="MK1" s="3" t="inlineStr">
+      <c r="MP1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="ML1" s="3" t="inlineStr">
+      <c r="MQ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3ChangeReasonActionCode</t>
         </is>
       </c>
-      <c r="MM1" s="3" t="inlineStr">
+      <c r="MR1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3ChangeReasonEffectiveDate</t>
         </is>
       </c>
-      <c r="MN1" s="3" t="inlineStr">
+      <c r="MS1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageProvider3ChangeReasonReasonCode</t>
         </is>
       </c>
-      <c r="MO1" s="3" t="inlineStr">
+      <c r="MT1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1PayerResponsibilitySequenceCode</t>
         </is>
       </c>
-      <c r="MP1" s="3" t="inlineStr">
+      <c r="MU1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1PayerResponsibilitySequence</t>
         </is>
       </c>
-      <c r="MQ1" s="3" t="inlineStr">
+      <c r="MV1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1GroupOrPolicyNumber</t>
         </is>
       </c>
-      <c r="MR1" s="3" t="inlineStr">
+      <c r="MW1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1CoordinationOfBenefitsCode</t>
         </is>
       </c>
-      <c r="MS1" s="3" t="inlineStr">
+      <c r="MX1" s="3" t="inlineStr">
+        <is>
+          <t>HealthCoverageCob1ServiceTypeCode1</t>
+        </is>
+      </c>
+      <c r="MY1" s="3" t="inlineStr">
+        <is>
+          <t>HealthCoverageCob1ServiceTypeCode2</t>
+        </is>
+      </c>
+      <c r="MZ1" s="3" t="inlineStr">
+        <is>
+          <t>HealthCoverageCob1ServiceTypeCode3</t>
+        </is>
+      </c>
+      <c r="NA1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1AdditionalIdentifier1QualifierCode</t>
         </is>
       </c>
-      <c r="MT1" s="3" t="inlineStr">
+      <c r="NB1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1AdditionalIdentifier1Identification</t>
         </is>
       </c>
-      <c r="MU1" s="3" t="inlineStr">
+      <c r="NC1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1AdditionalIdentifier2QualifierCode</t>
         </is>
       </c>
-      <c r="MV1" s="3" t="inlineStr">
+      <c r="ND1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1AdditionalIdentifier2Identification</t>
         </is>
       </c>
-      <c r="MW1" s="3" t="inlineStr">
+      <c r="NE1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1DateFrom</t>
         </is>
       </c>
-      <c r="MX1" s="3" t="inlineStr">
+      <c r="NF1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1DateTo</t>
         </is>
       </c>
-      <c r="MY1" s="3" t="inlineStr">
+      <c r="NG1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1EntityRole</t>
         </is>
       </c>
-      <c r="MZ1" s="3" t="inlineStr">
+      <c r="NH1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1Identifier</t>
         </is>
       </c>
-      <c r="NA1" s="3" t="inlineStr">
+      <c r="NI1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1Name</t>
         </is>
       </c>
-      <c r="NB1" s="3" t="inlineStr">
+      <c r="NJ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1AddressLine</t>
         </is>
       </c>
-      <c r="NC1" s="3" t="inlineStr">
+      <c r="NK1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1AddressLine2</t>
         </is>
       </c>
-      <c r="ND1" s="3" t="inlineStr">
+      <c r="NL1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1AddressCity</t>
         </is>
       </c>
-      <c r="NE1" s="3" t="inlineStr">
+      <c r="NM1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1AddressStateCode</t>
         </is>
       </c>
-      <c r="NF1" s="3" t="inlineStr">
+      <c r="NN1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1AddressZipCode</t>
         </is>
       </c>
-      <c r="NG1" s="3" t="inlineStr">
+      <c r="NO1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="NH1" s="3" t="inlineStr">
+      <c r="NP1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="NI1" s="3" t="inlineStr">
+      <c r="NQ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="NJ1" s="3" t="inlineStr">
+      <c r="NR1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer1ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="NK1" s="3" t="inlineStr">
+      <c r="NS1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2EntityRole</t>
         </is>
       </c>
-      <c r="NL1" s="3" t="inlineStr">
+      <c r="NT1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2Identifier</t>
         </is>
       </c>
-      <c r="NM1" s="3" t="inlineStr">
+      <c r="NU1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2Name</t>
         </is>
       </c>
-      <c r="NN1" s="3" t="inlineStr">
+      <c r="NV1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2AddressLine</t>
         </is>
       </c>
-      <c r="NO1" s="3" t="inlineStr">
+      <c r="NW1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2AddressLine2</t>
         </is>
       </c>
-      <c r="NP1" s="3" t="inlineStr">
+      <c r="NX1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2AddressCity</t>
         </is>
       </c>
-      <c r="NQ1" s="3" t="inlineStr">
+      <c r="NY1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2AddressStateCode</t>
         </is>
       </c>
-      <c r="NR1" s="3" t="inlineStr">
+      <c r="NZ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2AddressZipCode</t>
         </is>
       </c>
-      <c r="NS1" s="3" t="inlineStr">
+      <c r="OA1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="NT1" s="3" t="inlineStr">
+      <c r="OB1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="NU1" s="3" t="inlineStr">
+      <c r="OC1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="NV1" s="3" t="inlineStr">
+      <c r="OD1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob1Insurer2ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="NW1" s="3" t="inlineStr">
+      <c r="OE1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2PayerResponsibilitySequenceCode</t>
         </is>
       </c>
-      <c r="NX1" s="3" t="inlineStr">
+      <c r="OF1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2PayerResponsibilitySequence</t>
         </is>
       </c>
-      <c r="NY1" s="3" t="inlineStr">
+      <c r="OG1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2GroupOrPolicyNumber</t>
         </is>
       </c>
-      <c r="NZ1" s="3" t="inlineStr">
+      <c r="OH1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2CoordinationOfBenefitsCode</t>
         </is>
       </c>
-      <c r="OA1" s="3" t="inlineStr">
+      <c r="OI1" s="3" t="inlineStr">
+        <is>
+          <t>HealthCoverageCob2ServiceTypeCode1</t>
+        </is>
+      </c>
+      <c r="OJ1" s="3" t="inlineStr">
+        <is>
+          <t>HealthCoverageCob2ServiceTypeCode2</t>
+        </is>
+      </c>
+      <c r="OK1" s="3" t="inlineStr">
+        <is>
+          <t>HealthCoverageCob2ServiceTypeCode3</t>
+        </is>
+      </c>
+      <c r="OL1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2AdditionalIdentifier1QualifierCode</t>
         </is>
       </c>
-      <c r="OB1" s="3" t="inlineStr">
+      <c r="OM1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2AdditionalIdentifier1Identification</t>
         </is>
       </c>
-      <c r="OC1" s="3" t="inlineStr">
+      <c r="ON1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2AdditionalIdentifier2QualifierCode</t>
         </is>
       </c>
-      <c r="OD1" s="3" t="inlineStr">
+      <c r="OO1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2AdditionalIdentifier2Identification</t>
         </is>
       </c>
-      <c r="OE1" s="3" t="inlineStr">
+      <c r="OP1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2DateFrom</t>
         </is>
       </c>
-      <c r="OF1" s="3" t="inlineStr">
+      <c r="OQ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2DateTo</t>
         </is>
       </c>
-      <c r="OG1" s="3" t="inlineStr">
+      <c r="OR1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1EntityRole</t>
         </is>
       </c>
-      <c r="OH1" s="3" t="inlineStr">
+      <c r="OS1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1Identifier</t>
         </is>
       </c>
-      <c r="OI1" s="3" t="inlineStr">
+      <c r="OT1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1Name</t>
         </is>
       </c>
-      <c r="OJ1" s="3" t="inlineStr">
+      <c r="OU1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1AddressLine</t>
         </is>
       </c>
-      <c r="OK1" s="3" t="inlineStr">
+      <c r="OV1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1AddressLine2</t>
         </is>
       </c>
-      <c r="OL1" s="3" t="inlineStr">
+      <c r="OW1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1AddressCity</t>
         </is>
       </c>
-      <c r="OM1" s="3" t="inlineStr">
+      <c r="OX1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1AddressStateCode</t>
         </is>
       </c>
-      <c r="ON1" s="3" t="inlineStr">
+      <c r="OY1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1AddressZipCode</t>
         </is>
       </c>
-      <c r="OO1" s="3" t="inlineStr">
+      <c r="OZ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="OP1" s="3" t="inlineStr">
+      <c r="PA1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="OQ1" s="3" t="inlineStr">
+      <c r="PB1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="OR1" s="3" t="inlineStr">
+      <c r="PC1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer1ContactContactNumber2Number</t>
         </is>
       </c>
-      <c r="OS1" s="3" t="inlineStr">
+      <c r="PD1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2EntityRole</t>
         </is>
       </c>
-      <c r="OT1" s="3" t="inlineStr">
+      <c r="PE1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2Identifier</t>
         </is>
       </c>
-      <c r="OU1" s="3" t="inlineStr">
+      <c r="PF1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2Name</t>
         </is>
       </c>
-      <c r="OV1" s="3" t="inlineStr">
+      <c r="PG1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2AddressLine</t>
         </is>
       </c>
-      <c r="OW1" s="3" t="inlineStr">
+      <c r="PH1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2AddressLine2</t>
         </is>
       </c>
-      <c r="OX1" s="3" t="inlineStr">
+      <c r="PI1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2AddressCity</t>
         </is>
       </c>
-      <c r="OY1" s="3" t="inlineStr">
+      <c r="PJ1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2AddressStateCode</t>
         </is>
       </c>
-      <c r="OZ1" s="3" t="inlineStr">
+      <c r="PK1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2AddressZipCode</t>
         </is>
       </c>
-      <c r="PA1" s="3" t="inlineStr">
+      <c r="PL1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2ContactContactNumber1Type</t>
         </is>
       </c>
-      <c r="PB1" s="3" t="inlineStr">
+      <c r="PM1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2ContactContactNumber1Number</t>
         </is>
       </c>
-      <c r="PC1" s="3" t="inlineStr">
+      <c r="PN1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2ContactContactNumber2Type</t>
         </is>
       </c>
-      <c r="PD1" s="3" t="inlineStr">
+      <c r="PO1" s="3" t="inlineStr">
         <is>
           <t>HealthCoverageCob2Insurer2ContactContactNumber2Number</t>
         </is>
@@ -2167,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fdb3</t>
+          <t>6976904ee9a75feb648550cb</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2253,28 +2308,28 @@
         </is>
       </c>
       <c r="AF2"/>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="AH2"/>
-      <c r="AI2"/>
       <c r="AJ2"/>
       <c r="AK2"/>
-      <c r="AL2" s="3" t="inlineStr">
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM2" s="3" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
       <c r="AQ2"/>
       <c r="AR2"/>
       <c r="AS2"/>
@@ -2282,56 +2337,56 @@
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
-      <c r="AX2" s="3" t="inlineStr">
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2" s="3" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="AY2" s="4" t="n">
+      <c r="BB2" s="4" t="n">
         <v>35339.0</v>
       </c>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
       <c r="BC2"/>
       <c r="BD2"/>
       <c r="BE2"/>
       <c r="BF2"/>
       <c r="BG2"/>
-      <c r="BH2" s="3" t="inlineStr">
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI2" s="3" t="inlineStr">
+      <c r="BL2" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ2" s="3" t="inlineStr">
+      <c r="BM2" s="3" t="inlineStr">
         <is>
           <t>103229876</t>
         </is>
       </c>
-      <c r="BK2"/>
-      <c r="BL2" s="3" t="inlineStr">
+      <c r="BN2"/>
+      <c r="BO2" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM2" s="3" t="inlineStr">
+      <c r="BP2" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="BN2" s="3" t="inlineStr">
+      <c r="BQ2" s="3" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
       <c r="BR2"/>
       <c r="BS2"/>
       <c r="BT2"/>
@@ -2683,11 +2738,22 @@
       <c r="PB2"/>
       <c r="PC2"/>
       <c r="PD2"/>
+      <c r="PE2"/>
+      <c r="PF2"/>
+      <c r="PG2"/>
+      <c r="PH2"/>
+      <c r="PI2"/>
+      <c r="PJ2"/>
+      <c r="PK2"/>
+      <c r="PL2"/>
+      <c r="PM2"/>
+      <c r="PN2"/>
+      <c r="PO2"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fdcc</t>
+          <t>6976904ee9a75feb648550e4</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2773,28 +2839,28 @@
         </is>
       </c>
       <c r="AF3"/>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH3"/>
-      <c r="AI3"/>
       <c r="AJ3"/>
       <c r="AK3"/>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AL3"/>
+      <c r="AM3"/>
+      <c r="AN3"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN3"/>
-      <c r="AO3"/>
-      <c r="AP3"/>
       <c r="AQ3"/>
       <c r="AR3"/>
       <c r="AS3"/>
@@ -2812,35 +2878,35 @@
       <c r="BE3"/>
       <c r="BF3"/>
       <c r="BG3"/>
-      <c r="BH3" s="3" t="inlineStr">
+      <c r="BH3"/>
+      <c r="BI3"/>
+      <c r="BJ3"/>
+      <c r="BK3" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI3" s="3" t="inlineStr">
+      <c r="BL3" s="3" t="inlineStr">
         <is>
           <t>MUTUALLY_DEFINED</t>
         </is>
       </c>
-      <c r="BJ3" s="3" t="inlineStr">
+      <c r="BM3" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="BK3"/>
-      <c r="BL3" s="3" t="inlineStr">
+      <c r="BN3"/>
+      <c r="BO3" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM3" s="3" t="inlineStr">
+      <c r="BP3" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN3"/>
-      <c r="BO3"/>
-      <c r="BP3"/>
       <c r="BQ3"/>
       <c r="BR3"/>
       <c r="BS3"/>
@@ -3035,32 +3101,32 @@
       <c r="IZ3"/>
       <c r="JA3"/>
       <c r="JB3"/>
-      <c r="JC3" s="3" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="JD3" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
+      <c r="JC3"/>
+      <c r="JD3"/>
       <c r="JE3"/>
       <c r="JF3"/>
       <c r="JG3"/>
       <c r="JH3" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI3" s="4" t="n">
-        <v>37438.0</v>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="JI3" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
       </c>
       <c r="JJ3"/>
       <c r="JK3"/>
       <c r="JL3"/>
-      <c r="JM3"/>
-      <c r="JN3"/>
+      <c r="JM3" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN3" s="4" t="n">
+        <v>37438.0</v>
+      </c>
       <c r="JO3"/>
       <c r="JP3"/>
       <c r="JQ3"/>
@@ -3207,11 +3273,22 @@
       <c r="PB3"/>
       <c r="PC3"/>
       <c r="PD3"/>
+      <c r="PE3"/>
+      <c r="PF3"/>
+      <c r="PG3"/>
+      <c r="PH3"/>
+      <c r="PI3"/>
+      <c r="PJ3"/>
+      <c r="PK3"/>
+      <c r="PL3"/>
+      <c r="PM3"/>
+      <c r="PN3"/>
+      <c r="PO3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fde3</t>
+          <t>6976904ee9a75feb648550fb</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3297,28 +3374,28 @@
         </is>
       </c>
       <c r="AF4"/>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH4"/>
-      <c r="AI4"/>
       <c r="AJ4"/>
       <c r="AK4"/>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN4"/>
-      <c r="AO4"/>
-      <c r="AP4"/>
       <c r="AQ4"/>
       <c r="AR4"/>
       <c r="AS4"/>
@@ -3336,35 +3413,35 @@
       <c r="BE4"/>
       <c r="BF4"/>
       <c r="BG4"/>
-      <c r="BH4" s="3" t="inlineStr">
+      <c r="BH4"/>
+      <c r="BI4"/>
+      <c r="BJ4"/>
+      <c r="BK4" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI4" s="3" t="inlineStr">
+      <c r="BL4" s="3" t="inlineStr">
         <is>
           <t>MUTUALLY_DEFINED</t>
         </is>
       </c>
-      <c r="BJ4" s="3" t="inlineStr">
+      <c r="BM4" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="BK4"/>
-      <c r="BL4" s="3" t="inlineStr">
+      <c r="BN4"/>
+      <c r="BO4" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM4" s="3" t="inlineStr">
+      <c r="BP4" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN4"/>
-      <c r="BO4"/>
-      <c r="BP4"/>
       <c r="BQ4"/>
       <c r="BR4"/>
       <c r="BS4"/>
@@ -3717,11 +3794,22 @@
       <c r="PB4"/>
       <c r="PC4"/>
       <c r="PD4"/>
+      <c r="PE4"/>
+      <c r="PF4"/>
+      <c r="PG4"/>
+      <c r="PH4"/>
+      <c r="PI4"/>
+      <c r="PJ4"/>
+      <c r="PK4"/>
+      <c r="PL4"/>
+      <c r="PM4"/>
+      <c r="PN4"/>
+      <c r="PO4"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fe3f</t>
+          <t>6976904ee9a75feb64855157</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3807,28 +3895,28 @@
         </is>
       </c>
       <c r="AF5"/>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH5"/>
-      <c r="AI5"/>
       <c r="AJ5"/>
       <c r="AK5"/>
-      <c r="AL5" s="3" t="inlineStr">
+      <c r="AL5"/>
+      <c r="AM5"/>
+      <c r="AN5"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>member1</t>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="AN5"/>
-      <c r="AO5"/>
-      <c r="AP5"/>
       <c r="AQ5"/>
       <c r="AR5"/>
       <c r="AS5"/>
@@ -3836,101 +3924,101 @@
       <c r="AU5"/>
       <c r="AV5"/>
       <c r="AW5"/>
-      <c r="AX5" s="3" t="inlineStr">
+      <c r="AX5"/>
+      <c r="AY5"/>
+      <c r="AZ5"/>
+      <c r="BA5" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY5" s="4" t="n">
+      <c r="BB5" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ5"/>
-      <c r="BA5"/>
-      <c r="BB5"/>
       <c r="BC5"/>
       <c r="BD5"/>
       <c r="BE5"/>
       <c r="BF5"/>
       <c r="BG5"/>
-      <c r="BH5" s="3" t="inlineStr">
+      <c r="BH5"/>
+      <c r="BI5"/>
+      <c r="BJ5"/>
+      <c r="BK5" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI5" s="3" t="inlineStr">
+      <c r="BL5" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ5" s="3" t="inlineStr">
+      <c r="BM5" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="BK5"/>
-      <c r="BL5" s="3" t="inlineStr">
+      <c r="BN5"/>
+      <c r="BO5" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM5" s="3" t="inlineStr">
+      <c r="BP5" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN5"/>
-      <c r="BO5" s="4" t="n">
+      <c r="BQ5"/>
+      <c r="BR5" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP5" s="3" t="inlineStr">
+      <c r="BS5" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ5" s="3" t="inlineStr">
+      <c r="BT5" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR5"/>
-      <c r="BS5" s="3" t="inlineStr">
+      <c r="BU5"/>
+      <c r="BV5" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT5" s="3" t="inlineStr">
+      <c r="BW5" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU5" s="3" t="inlineStr">
+      <c r="BX5" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV5" s="3" t="inlineStr">
+      <c r="BY5" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW5" s="3" t="inlineStr">
+      <c r="BZ5" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX5" s="3" t="inlineStr">
+      <c r="CA5" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY5" s="3" t="inlineStr">
+      <c r="CB5" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ5"/>
-      <c r="CA5"/>
-      <c r="CB5"/>
       <c r="CC5"/>
       <c r="CD5"/>
       <c r="CE5"/>
@@ -4113,32 +4201,32 @@
       <c r="IZ5"/>
       <c r="JA5"/>
       <c r="JB5"/>
-      <c r="JC5" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD5" s="3" t="inlineStr">
-        <is>
-          <t>HMO</t>
-        </is>
-      </c>
+      <c r="JC5"/>
+      <c r="JD5"/>
       <c r="JE5"/>
       <c r="JF5"/>
       <c r="JG5"/>
       <c r="JH5" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI5" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI5" s="3" t="inlineStr">
+        <is>
+          <t>HMO</t>
+        </is>
       </c>
       <c r="JJ5"/>
       <c r="JK5"/>
       <c r="JL5"/>
-      <c r="JM5"/>
-      <c r="JN5"/>
+      <c r="JM5" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN5" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO5"/>
       <c r="JP5"/>
       <c r="JQ5"/>
@@ -4163,59 +4251,59 @@
       <c r="KJ5"/>
       <c r="KK5"/>
       <c r="KL5"/>
-      <c r="KM5" s="3" t="inlineStr">
+      <c r="KM5"/>
+      <c r="KN5"/>
+      <c r="KO5"/>
+      <c r="KP5"/>
+      <c r="KQ5"/>
+      <c r="KR5" s="3" t="inlineStr">
         <is>
           <t>PRIMARY_CARE</t>
         </is>
       </c>
-      <c r="KN5" s="3" t="inlineStr">
+      <c r="KS5" s="3" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="KO5" s="3" t="inlineStr">
+      <c r="KT5" s="3" t="inlineStr">
         <is>
           <t>143766</t>
         </is>
       </c>
-      <c r="KP5" s="3" t="inlineStr">
+      <c r="KU5" s="3" t="inlineStr">
         <is>
           <t>BROWN</t>
         </is>
       </c>
-      <c r="KQ5" s="3" t="inlineStr">
+      <c r="KV5" s="3" t="inlineStr">
         <is>
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="KR5"/>
-      <c r="KS5"/>
-      <c r="KT5"/>
-      <c r="KU5"/>
-      <c r="KV5"/>
       <c r="KW5"/>
       <c r="KX5"/>
       <c r="KY5"/>
       <c r="KZ5"/>
       <c r="LA5"/>
-      <c r="LB5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="LC5" s="4" t="n">
-        <v>45413.0</v>
-      </c>
-      <c r="LD5" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+      <c r="LB5"/>
+      <c r="LC5"/>
+      <c r="LD5"/>
       <c r="LE5"/>
       <c r="LF5"/>
-      <c r="LG5"/>
-      <c r="LH5"/>
-      <c r="LI5"/>
+      <c r="LG5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="LH5" s="4" t="n">
+        <v>45413.0</v>
+      </c>
+      <c r="LI5" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
       <c r="LJ5"/>
       <c r="LK5"/>
       <c r="LL5"/>
@@ -4315,11 +4403,22 @@
       <c r="PB5"/>
       <c r="PC5"/>
       <c r="PD5"/>
+      <c r="PE5"/>
+      <c r="PF5"/>
+      <c r="PG5"/>
+      <c r="PH5"/>
+      <c r="PI5"/>
+      <c r="PJ5"/>
+      <c r="PK5"/>
+      <c r="PL5"/>
+      <c r="PM5"/>
+      <c r="PN5"/>
+      <c r="PO5"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fe40</t>
+          <t>6976904ee9a75feb64855158</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4405,28 +4504,28 @@
         </is>
       </c>
       <c r="AF6"/>
-      <c r="AG6" s="3" t="inlineStr">
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH6"/>
-      <c r="AI6"/>
       <c r="AJ6"/>
       <c r="AK6"/>
-      <c r="AL6" s="3" t="inlineStr">
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>member2</t>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="AN6"/>
-      <c r="AO6"/>
-      <c r="AP6"/>
       <c r="AQ6"/>
       <c r="AR6"/>
       <c r="AS6"/>
@@ -4434,101 +4533,101 @@
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6"/>
-      <c r="AX6" s="3" t="inlineStr">
+      <c r="AX6"/>
+      <c r="AY6"/>
+      <c r="AZ6"/>
+      <c r="BA6" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY6" s="4" t="n">
+      <c r="BB6" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ6"/>
-      <c r="BA6"/>
-      <c r="BB6"/>
       <c r="BC6"/>
       <c r="BD6"/>
       <c r="BE6"/>
       <c r="BF6"/>
       <c r="BG6"/>
-      <c r="BH6" s="3" t="inlineStr">
+      <c r="BH6"/>
+      <c r="BI6"/>
+      <c r="BJ6"/>
+      <c r="BK6" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI6" s="3" t="inlineStr">
+      <c r="BL6" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ6" s="3" t="inlineStr">
+      <c r="BM6" s="3" t="inlineStr">
         <is>
           <t>202443309</t>
         </is>
       </c>
-      <c r="BK6"/>
-      <c r="BL6" s="3" t="inlineStr">
+      <c r="BN6"/>
+      <c r="BO6" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM6" s="3" t="inlineStr">
+      <c r="BP6" s="3" t="inlineStr">
         <is>
           <t>Jane</t>
         </is>
       </c>
-      <c r="BN6"/>
-      <c r="BO6" s="4" t="n">
+      <c r="BQ6"/>
+      <c r="BR6" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP6" s="3" t="inlineStr">
+      <c r="BS6" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ6" s="3" t="inlineStr">
+      <c r="BT6" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR6"/>
-      <c r="BS6" s="3" t="inlineStr">
+      <c r="BU6"/>
+      <c r="BV6" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT6" s="3" t="inlineStr">
+      <c r="BW6" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU6" s="3" t="inlineStr">
+      <c r="BX6" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV6" s="3" t="inlineStr">
+      <c r="BY6" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW6" s="3" t="inlineStr">
+      <c r="BZ6" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX6" s="3" t="inlineStr">
+      <c r="CA6" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY6" s="3" t="inlineStr">
+      <c r="CB6" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ6"/>
-      <c r="CA6"/>
-      <c r="CB6"/>
       <c r="CC6"/>
       <c r="CD6"/>
       <c r="CE6"/>
@@ -4711,32 +4810,32 @@
       <c r="IZ6"/>
       <c r="JA6"/>
       <c r="JB6"/>
-      <c r="JC6" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD6" s="3" t="inlineStr">
-        <is>
-          <t>HMO</t>
-        </is>
-      </c>
+      <c r="JC6"/>
+      <c r="JD6"/>
       <c r="JE6"/>
       <c r="JF6"/>
       <c r="JG6"/>
       <c r="JH6" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI6" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI6" s="3" t="inlineStr">
+        <is>
+          <t>HMO</t>
+        </is>
       </c>
       <c r="JJ6"/>
       <c r="JK6"/>
       <c r="JL6"/>
-      <c r="JM6"/>
-      <c r="JN6"/>
+      <c r="JM6" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN6" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO6"/>
       <c r="JP6"/>
       <c r="JQ6"/>
@@ -4761,59 +4860,59 @@
       <c r="KJ6"/>
       <c r="KK6"/>
       <c r="KL6"/>
-      <c r="KM6" s="3" t="inlineStr">
+      <c r="KM6"/>
+      <c r="KN6"/>
+      <c r="KO6"/>
+      <c r="KP6"/>
+      <c r="KQ6"/>
+      <c r="KR6" s="3" t="inlineStr">
         <is>
           <t>PRIMARY_CARE</t>
         </is>
       </c>
-      <c r="KN6" s="3" t="inlineStr">
+      <c r="KS6" s="3" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="KO6" s="3" t="inlineStr">
+      <c r="KT6" s="3" t="inlineStr">
         <is>
           <t>143766</t>
         </is>
       </c>
-      <c r="KP6" s="3" t="inlineStr">
+      <c r="KU6" s="3" t="inlineStr">
         <is>
           <t>BROWN</t>
         </is>
       </c>
-      <c r="KQ6" s="3" t="inlineStr">
+      <c r="KV6" s="3" t="inlineStr">
         <is>
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="KR6"/>
-      <c r="KS6"/>
-      <c r="KT6"/>
-      <c r="KU6"/>
-      <c r="KV6"/>
       <c r="KW6"/>
       <c r="KX6"/>
       <c r="KY6"/>
       <c r="KZ6"/>
       <c r="LA6"/>
-      <c r="LB6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="LC6" s="4" t="n">
-        <v>45413.0</v>
-      </c>
-      <c r="LD6" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+      <c r="LB6"/>
+      <c r="LC6"/>
+      <c r="LD6"/>
       <c r="LE6"/>
       <c r="LF6"/>
-      <c r="LG6"/>
-      <c r="LH6"/>
-      <c r="LI6"/>
+      <c r="LG6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="LH6" s="4" t="n">
+        <v>45413.0</v>
+      </c>
+      <c r="LI6" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
       <c r="LJ6"/>
       <c r="LK6"/>
       <c r="LL6"/>
@@ -4913,11 +5012,22 @@
       <c r="PB6"/>
       <c r="PC6"/>
       <c r="PD6"/>
+      <c r="PE6"/>
+      <c r="PF6"/>
+      <c r="PG6"/>
+      <c r="PH6"/>
+      <c r="PI6"/>
+      <c r="PJ6"/>
+      <c r="PK6"/>
+      <c r="PL6"/>
+      <c r="PM6"/>
+      <c r="PN6"/>
+      <c r="PO6"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fe41</t>
+          <t>6976904ee9a75feb64855159</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5003,28 +5113,28 @@
         </is>
       </c>
       <c r="AF7"/>
-      <c r="AG7" s="3" t="inlineStr">
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH7"/>
-      <c r="AI7"/>
       <c r="AJ7"/>
       <c r="AK7"/>
-      <c r="AL7" s="3" t="inlineStr">
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>member3</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="inlineStr">
+      <c r="AP7" s="3" t="inlineStr">
         <is>
           <t>group3</t>
         </is>
       </c>
-      <c r="AN7"/>
-      <c r="AO7"/>
-      <c r="AP7"/>
       <c r="AQ7"/>
       <c r="AR7"/>
       <c r="AS7"/>
@@ -5032,101 +5142,101 @@
       <c r="AU7"/>
       <c r="AV7"/>
       <c r="AW7"/>
-      <c r="AX7" s="3" t="inlineStr">
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+      <c r="BA7" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY7" s="4" t="n">
+      <c r="BB7" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ7"/>
-      <c r="BA7"/>
-      <c r="BB7"/>
       <c r="BC7"/>
       <c r="BD7"/>
       <c r="BE7"/>
       <c r="BF7"/>
       <c r="BG7"/>
-      <c r="BH7" s="3" t="inlineStr">
+      <c r="BH7"/>
+      <c r="BI7"/>
+      <c r="BJ7"/>
+      <c r="BK7" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI7" s="3" t="inlineStr">
+      <c r="BL7" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ7" s="3" t="inlineStr">
+      <c r="BM7" s="3" t="inlineStr">
         <is>
           <t>202443327</t>
         </is>
       </c>
-      <c r="BK7"/>
-      <c r="BL7" s="3" t="inlineStr">
+      <c r="BN7"/>
+      <c r="BO7" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM7" s="3" t="inlineStr">
+      <c r="BP7" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN7"/>
-      <c r="BO7" s="4" t="n">
+      <c r="BQ7"/>
+      <c r="BR7" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP7" s="3" t="inlineStr">
+      <c r="BS7" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ7" s="3" t="inlineStr">
+      <c r="BT7" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR7"/>
-      <c r="BS7" s="3" t="inlineStr">
+      <c r="BU7"/>
+      <c r="BV7" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT7" s="3" t="inlineStr">
+      <c r="BW7" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU7" s="3" t="inlineStr">
+      <c r="BX7" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV7" s="3" t="inlineStr">
+      <c r="BY7" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW7" s="3" t="inlineStr">
+      <c r="BZ7" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX7" s="3" t="inlineStr">
+      <c r="CA7" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY7" s="3" t="inlineStr">
+      <c r="CB7" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ7"/>
-      <c r="CA7"/>
-      <c r="CB7"/>
       <c r="CC7"/>
       <c r="CD7"/>
       <c r="CE7"/>
@@ -5309,32 +5419,32 @@
       <c r="IZ7"/>
       <c r="JA7"/>
       <c r="JB7"/>
-      <c r="JC7" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD7" s="3" t="inlineStr">
-        <is>
-          <t>HMO</t>
-        </is>
-      </c>
+      <c r="JC7"/>
+      <c r="JD7"/>
       <c r="JE7"/>
       <c r="JF7"/>
       <c r="JG7"/>
       <c r="JH7" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI7" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI7" s="3" t="inlineStr">
+        <is>
+          <t>HMO</t>
+        </is>
       </c>
       <c r="JJ7"/>
       <c r="JK7"/>
       <c r="JL7"/>
-      <c r="JM7"/>
-      <c r="JN7"/>
+      <c r="JM7" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN7" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO7"/>
       <c r="JP7"/>
       <c r="JQ7"/>
@@ -5359,59 +5469,59 @@
       <c r="KJ7"/>
       <c r="KK7"/>
       <c r="KL7"/>
-      <c r="KM7" s="3" t="inlineStr">
+      <c r="KM7"/>
+      <c r="KN7"/>
+      <c r="KO7"/>
+      <c r="KP7"/>
+      <c r="KQ7"/>
+      <c r="KR7" s="3" t="inlineStr">
         <is>
           <t>PRIMARY_CARE</t>
         </is>
       </c>
-      <c r="KN7" s="3" t="inlineStr">
+      <c r="KS7" s="3" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="KO7" s="3" t="inlineStr">
+      <c r="KT7" s="3" t="inlineStr">
         <is>
           <t>143766</t>
         </is>
       </c>
-      <c r="KP7" s="3" t="inlineStr">
+      <c r="KU7" s="3" t="inlineStr">
         <is>
           <t>BROWN</t>
         </is>
       </c>
-      <c r="KQ7" s="3" t="inlineStr">
+      <c r="KV7" s="3" t="inlineStr">
         <is>
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="KR7"/>
-      <c r="KS7"/>
-      <c r="KT7"/>
-      <c r="KU7"/>
-      <c r="KV7"/>
       <c r="KW7"/>
       <c r="KX7"/>
       <c r="KY7"/>
       <c r="KZ7"/>
       <c r="LA7"/>
-      <c r="LB7" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="LC7" s="4" t="n">
-        <v>45413.0</v>
-      </c>
-      <c r="LD7" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+      <c r="LB7"/>
+      <c r="LC7"/>
+      <c r="LD7"/>
       <c r="LE7"/>
       <c r="LF7"/>
-      <c r="LG7"/>
-      <c r="LH7"/>
-      <c r="LI7"/>
+      <c r="LG7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="LH7" s="4" t="n">
+        <v>45413.0</v>
+      </c>
+      <c r="LI7" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
       <c r="LJ7"/>
       <c r="LK7"/>
       <c r="LL7"/>
@@ -5511,11 +5621,22 @@
       <c r="PB7"/>
       <c r="PC7"/>
       <c r="PD7"/>
+      <c r="PE7"/>
+      <c r="PF7"/>
+      <c r="PG7"/>
+      <c r="PH7"/>
+      <c r="PI7"/>
+      <c r="PJ7"/>
+      <c r="PK7"/>
+      <c r="PL7"/>
+      <c r="PM7"/>
+      <c r="PN7"/>
+      <c r="PO7"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fe42</t>
+          <t>6976904ee9a75feb6485515a</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -5601,28 +5722,28 @@
         </is>
       </c>
       <c r="AF8"/>
-      <c r="AG8" s="3" t="inlineStr">
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH8"/>
-      <c r="AI8"/>
       <c r="AJ8"/>
       <c r="AK8"/>
-      <c r="AL8" s="3" t="inlineStr">
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>member4</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr">
         <is>
           <t>group4</t>
         </is>
       </c>
-      <c r="AN8"/>
-      <c r="AO8"/>
-      <c r="AP8"/>
       <c r="AQ8"/>
       <c r="AR8"/>
       <c r="AS8"/>
@@ -5630,101 +5751,101 @@
       <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8"/>
-      <c r="AX8" s="3" t="inlineStr">
+      <c r="AX8"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+      <c r="BA8" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY8" s="4" t="n">
+      <c r="BB8" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ8"/>
-      <c r="BA8"/>
-      <c r="BB8"/>
       <c r="BC8"/>
       <c r="BD8"/>
       <c r="BE8"/>
       <c r="BF8"/>
       <c r="BG8"/>
-      <c r="BH8" s="3" t="inlineStr">
+      <c r="BH8"/>
+      <c r="BI8"/>
+      <c r="BJ8"/>
+      <c r="BK8" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI8" s="3" t="inlineStr">
+      <c r="BL8" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ8" s="3" t="inlineStr">
+      <c r="BM8" s="3" t="inlineStr">
         <is>
           <t>202443329</t>
         </is>
       </c>
-      <c r="BK8"/>
-      <c r="BL8" s="3" t="inlineStr">
+      <c r="BN8"/>
+      <c r="BO8" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM8" s="3" t="inlineStr">
+      <c r="BP8" s="3" t="inlineStr">
         <is>
           <t>Jane</t>
         </is>
       </c>
-      <c r="BN8"/>
-      <c r="BO8" s="4" t="n">
+      <c r="BQ8"/>
+      <c r="BR8" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP8" s="3" t="inlineStr">
+      <c r="BS8" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ8" s="3" t="inlineStr">
+      <c r="BT8" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR8"/>
-      <c r="BS8" s="3" t="inlineStr">
+      <c r="BU8"/>
+      <c r="BV8" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT8" s="3" t="inlineStr">
+      <c r="BW8" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU8" s="3" t="inlineStr">
+      <c r="BX8" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV8" s="3" t="inlineStr">
+      <c r="BY8" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW8" s="3" t="inlineStr">
+      <c r="BZ8" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX8" s="3" t="inlineStr">
+      <c r="CA8" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY8" s="3" t="inlineStr">
+      <c r="CB8" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ8"/>
-      <c r="CA8"/>
-      <c r="CB8"/>
       <c r="CC8"/>
       <c r="CD8"/>
       <c r="CE8"/>
@@ -5907,32 +6028,32 @@
       <c r="IZ8"/>
       <c r="JA8"/>
       <c r="JB8"/>
-      <c r="JC8" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD8" s="3" t="inlineStr">
-        <is>
-          <t>HMO</t>
-        </is>
-      </c>
+      <c r="JC8"/>
+      <c r="JD8"/>
       <c r="JE8"/>
       <c r="JF8"/>
       <c r="JG8"/>
       <c r="JH8" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI8" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI8" s="3" t="inlineStr">
+        <is>
+          <t>HMO</t>
+        </is>
       </c>
       <c r="JJ8"/>
       <c r="JK8"/>
       <c r="JL8"/>
-      <c r="JM8"/>
-      <c r="JN8"/>
+      <c r="JM8" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN8" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO8"/>
       <c r="JP8"/>
       <c r="JQ8"/>
@@ -5957,59 +6078,59 @@
       <c r="KJ8"/>
       <c r="KK8"/>
       <c r="KL8"/>
-      <c r="KM8" s="3" t="inlineStr">
+      <c r="KM8"/>
+      <c r="KN8"/>
+      <c r="KO8"/>
+      <c r="KP8"/>
+      <c r="KQ8"/>
+      <c r="KR8" s="3" t="inlineStr">
         <is>
           <t>PRIMARY_CARE</t>
         </is>
       </c>
-      <c r="KN8" s="3" t="inlineStr">
+      <c r="KS8" s="3" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="KO8" s="3" t="inlineStr">
+      <c r="KT8" s="3" t="inlineStr">
         <is>
           <t>143766</t>
         </is>
       </c>
-      <c r="KP8" s="3" t="inlineStr">
+      <c r="KU8" s="3" t="inlineStr">
         <is>
           <t>BROWN</t>
         </is>
       </c>
-      <c r="KQ8" s="3" t="inlineStr">
+      <c r="KV8" s="3" t="inlineStr">
         <is>
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="KR8"/>
-      <c r="KS8"/>
-      <c r="KT8"/>
-      <c r="KU8"/>
-      <c r="KV8"/>
       <c r="KW8"/>
       <c r="KX8"/>
       <c r="KY8"/>
       <c r="KZ8"/>
       <c r="LA8"/>
-      <c r="LB8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="LC8" s="4" t="n">
-        <v>45413.0</v>
-      </c>
-      <c r="LD8" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+      <c r="LB8"/>
+      <c r="LC8"/>
+      <c r="LD8"/>
       <c r="LE8"/>
       <c r="LF8"/>
-      <c r="LG8"/>
-      <c r="LH8"/>
-      <c r="LI8"/>
+      <c r="LG8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="LH8" s="4" t="n">
+        <v>45413.0</v>
+      </c>
+      <c r="LI8" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
       <c r="LJ8"/>
       <c r="LK8"/>
       <c r="LL8"/>
@@ -6109,11 +6230,22 @@
       <c r="PB8"/>
       <c r="PC8"/>
       <c r="PD8"/>
+      <c r="PE8"/>
+      <c r="PF8"/>
+      <c r="PG8"/>
+      <c r="PH8"/>
+      <c r="PI8"/>
+      <c r="PJ8"/>
+      <c r="PK8"/>
+      <c r="PL8"/>
+      <c r="PM8"/>
+      <c r="PN8"/>
+      <c r="PO8"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fe64</t>
+          <t>6976904ee9a75feb6485517c</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6199,28 +6331,28 @@
         </is>
       </c>
       <c r="AF9"/>
-      <c r="AG9" s="3" t="inlineStr">
+      <c r="AG9"/>
+      <c r="AH9"/>
+      <c r="AI9" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH9"/>
-      <c r="AI9"/>
       <c r="AJ9"/>
       <c r="AK9"/>
-      <c r="AL9" s="3" t="inlineStr">
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
+      <c r="AP9" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN9"/>
-      <c r="AO9"/>
-      <c r="AP9"/>
       <c r="AQ9"/>
       <c r="AR9"/>
       <c r="AS9"/>
@@ -6228,109 +6360,109 @@
       <c r="AU9"/>
       <c r="AV9"/>
       <c r="AW9"/>
-      <c r="AX9" s="3" t="inlineStr">
+      <c r="AX9"/>
+      <c r="AY9"/>
+      <c r="AZ9"/>
+      <c r="BA9" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY9" s="4" t="n">
+      <c r="BB9" s="4" t="n">
         <v>35208.0</v>
       </c>
-      <c r="AZ9"/>
-      <c r="BA9"/>
-      <c r="BB9"/>
       <c r="BC9"/>
       <c r="BD9"/>
       <c r="BE9"/>
       <c r="BF9"/>
       <c r="BG9"/>
-      <c r="BH9" s="3" t="inlineStr">
+      <c r="BH9"/>
+      <c r="BI9"/>
+      <c r="BJ9"/>
+      <c r="BK9" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI9" s="3" t="inlineStr">
+      <c r="BL9" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ9" s="3" t="inlineStr">
+      <c r="BM9" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="BK9"/>
-      <c r="BL9" s="3" t="inlineStr">
+      <c r="BN9"/>
+      <c r="BO9" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM9" s="3" t="inlineStr">
+      <c r="BP9" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="BN9" s="3" t="inlineStr">
+      <c r="BQ9" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="BO9" s="4" t="n">
+      <c r="BR9" s="4" t="n">
         <v>14839.0</v>
       </c>
-      <c r="BP9" s="3" t="inlineStr">
+      <c r="BS9" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ9" s="3" t="inlineStr">
+      <c r="BT9" s="3" t="inlineStr">
         <is>
           <t>100 MARKET ST</t>
         </is>
       </c>
-      <c r="BR9" s="3" t="inlineStr">
+      <c r="BU9" s="3" t="inlineStr">
         <is>
           <t>APT 3G</t>
         </is>
       </c>
-      <c r="BS9" s="3" t="inlineStr">
+      <c r="BV9" s="3" t="inlineStr">
         <is>
           <t>CAMP HILL</t>
         </is>
       </c>
-      <c r="BT9" s="3" t="inlineStr">
+      <c r="BW9" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU9" s="3" t="inlineStr">
+      <c r="BX9" s="3" t="inlineStr">
         <is>
           <t>17011</t>
         </is>
       </c>
-      <c r="BV9" s="3" t="inlineStr">
+      <c r="BY9" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW9" s="3" t="inlineStr">
+      <c r="BZ9" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX9" s="3" t="inlineStr">
+      <c r="CA9" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY9" s="3" t="inlineStr">
+      <c r="CB9" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ9"/>
-      <c r="CA9"/>
-      <c r="CB9"/>
       <c r="CC9"/>
       <c r="CD9"/>
       <c r="CE9"/>
@@ -6513,32 +6645,32 @@
       <c r="IZ9"/>
       <c r="JA9"/>
       <c r="JB9"/>
-      <c r="JC9" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD9" s="3" t="inlineStr">
-        <is>
-          <t>HLT</t>
-        </is>
-      </c>
+      <c r="JC9"/>
+      <c r="JD9"/>
       <c r="JE9"/>
       <c r="JF9"/>
       <c r="JG9"/>
       <c r="JH9" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI9" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI9" s="3" t="inlineStr">
+        <is>
+          <t>HLT</t>
+        </is>
       </c>
       <c r="JJ9"/>
       <c r="JK9"/>
       <c r="JL9"/>
-      <c r="JM9"/>
-      <c r="JN9"/>
+      <c r="JM9" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN9" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO9"/>
       <c r="JP9"/>
       <c r="JQ9"/>
@@ -6617,31 +6749,31 @@
       <c r="ML9"/>
       <c r="MM9"/>
       <c r="MN9"/>
-      <c r="MO9" s="3" t="inlineStr">
+      <c r="MO9"/>
+      <c r="MP9"/>
+      <c r="MQ9"/>
+      <c r="MR9"/>
+      <c r="MS9"/>
+      <c r="MT9" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="MP9" s="3" t="inlineStr">
+      <c r="MU9" s="3" t="inlineStr">
         <is>
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="MQ9" s="3" t="inlineStr">
+      <c r="MV9" s="3" t="inlineStr">
         <is>
           <t>890111</t>
         </is>
       </c>
-      <c r="MR9" s="3" t="inlineStr">
+      <c r="MW9" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="MS9"/>
-      <c r="MT9"/>
-      <c r="MU9"/>
-      <c r="MV9"/>
-      <c r="MW9"/>
       <c r="MX9"/>
       <c r="MY9"/>
       <c r="MZ9"/>
@@ -6701,11 +6833,22 @@
       <c r="PB9"/>
       <c r="PC9"/>
       <c r="PD9"/>
+      <c r="PE9"/>
+      <c r="PF9"/>
+      <c r="PG9"/>
+      <c r="PH9"/>
+      <c r="PI9"/>
+      <c r="PJ9"/>
+      <c r="PK9"/>
+      <c r="PL9"/>
+      <c r="PM9"/>
+      <c r="PN9"/>
+      <c r="PO9"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fe64</t>
+          <t>6976904ee9a75feb6485517c</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -6791,28 +6934,28 @@
         </is>
       </c>
       <c r="AF10"/>
-      <c r="AG10" s="3" t="inlineStr">
+      <c r="AG10"/>
+      <c r="AH10"/>
+      <c r="AI10" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH10"/>
-      <c r="AI10"/>
       <c r="AJ10"/>
       <c r="AK10"/>
-      <c r="AL10" s="3" t="inlineStr">
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
+      <c r="AP10" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN10"/>
-      <c r="AO10"/>
-      <c r="AP10"/>
       <c r="AQ10"/>
       <c r="AR10"/>
       <c r="AS10"/>
@@ -6820,109 +6963,109 @@
       <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
-      <c r="AX10" s="3" t="inlineStr">
+      <c r="AX10"/>
+      <c r="AY10"/>
+      <c r="AZ10"/>
+      <c r="BA10" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY10" s="4" t="n">
+      <c r="BB10" s="4" t="n">
         <v>35208.0</v>
       </c>
-      <c r="AZ10"/>
-      <c r="BA10"/>
-      <c r="BB10"/>
       <c r="BC10"/>
       <c r="BD10"/>
       <c r="BE10"/>
       <c r="BF10"/>
       <c r="BG10"/>
-      <c r="BH10" s="3" t="inlineStr">
+      <c r="BH10"/>
+      <c r="BI10"/>
+      <c r="BJ10"/>
+      <c r="BK10" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI10" s="3" t="inlineStr">
+      <c r="BL10" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ10" s="3" t="inlineStr">
+      <c r="BM10" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="BK10"/>
-      <c r="BL10" s="3" t="inlineStr">
+      <c r="BN10"/>
+      <c r="BO10" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM10" s="3" t="inlineStr">
+      <c r="BP10" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="BN10" s="3" t="inlineStr">
+      <c r="BQ10" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="BO10" s="4" t="n">
+      <c r="BR10" s="4" t="n">
         <v>14839.0</v>
       </c>
-      <c r="BP10" s="3" t="inlineStr">
+      <c r="BS10" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ10" s="3" t="inlineStr">
+      <c r="BT10" s="3" t="inlineStr">
         <is>
           <t>100 MARKET ST</t>
         </is>
       </c>
-      <c r="BR10" s="3" t="inlineStr">
+      <c r="BU10" s="3" t="inlineStr">
         <is>
           <t>APT 3G</t>
         </is>
       </c>
-      <c r="BS10" s="3" t="inlineStr">
+      <c r="BV10" s="3" t="inlineStr">
         <is>
           <t>CAMP HILL</t>
         </is>
       </c>
-      <c r="BT10" s="3" t="inlineStr">
+      <c r="BW10" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU10" s="3" t="inlineStr">
+      <c r="BX10" s="3" t="inlineStr">
         <is>
           <t>17011</t>
         </is>
       </c>
-      <c r="BV10" s="3" t="inlineStr">
+      <c r="BY10" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW10" s="3" t="inlineStr">
+      <c r="BZ10" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX10" s="3" t="inlineStr">
+      <c r="CA10" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY10" s="3" t="inlineStr">
+      <c r="CB10" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ10"/>
-      <c r="CA10"/>
-      <c r="CB10"/>
       <c r="CC10"/>
       <c r="CD10"/>
       <c r="CE10"/>
@@ -7105,32 +7248,32 @@
       <c r="IZ10"/>
       <c r="JA10"/>
       <c r="JB10"/>
-      <c r="JC10" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD10" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
+      <c r="JC10"/>
+      <c r="JD10"/>
       <c r="JE10"/>
       <c r="JF10"/>
       <c r="JG10"/>
       <c r="JH10" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI10" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI10" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
       </c>
       <c r="JJ10"/>
       <c r="JK10"/>
       <c r="JL10"/>
-      <c r="JM10"/>
-      <c r="JN10"/>
+      <c r="JM10" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN10" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO10"/>
       <c r="JP10"/>
       <c r="JQ10"/>
@@ -7277,11 +7420,22 @@
       <c r="PB10"/>
       <c r="PC10"/>
       <c r="PD10"/>
+      <c r="PE10"/>
+      <c r="PF10"/>
+      <c r="PG10"/>
+      <c r="PH10"/>
+      <c r="PI10"/>
+      <c r="PJ10"/>
+      <c r="PK10"/>
+      <c r="PL10"/>
+      <c r="PM10"/>
+      <c r="PN10"/>
+      <c r="PO10"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fe64</t>
+          <t>6976904ee9a75feb6485517c</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7367,28 +7521,28 @@
         </is>
       </c>
       <c r="AF11"/>
-      <c r="AG11" s="3" t="inlineStr">
+      <c r="AG11"/>
+      <c r="AH11"/>
+      <c r="AI11" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH11"/>
-      <c r="AI11"/>
       <c r="AJ11"/>
       <c r="AK11"/>
-      <c r="AL11" s="3" t="inlineStr">
+      <c r="AL11"/>
+      <c r="AM11"/>
+      <c r="AN11"/>
+      <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM11" s="3" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN11"/>
-      <c r="AO11"/>
-      <c r="AP11"/>
       <c r="AQ11"/>
       <c r="AR11"/>
       <c r="AS11"/>
@@ -7396,109 +7550,109 @@
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
-      <c r="AX11" s="3" t="inlineStr">
+      <c r="AX11"/>
+      <c r="AY11"/>
+      <c r="AZ11"/>
+      <c r="BA11" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY11" s="4" t="n">
+      <c r="BB11" s="4" t="n">
         <v>35208.0</v>
       </c>
-      <c r="AZ11"/>
-      <c r="BA11"/>
-      <c r="BB11"/>
       <c r="BC11"/>
       <c r="BD11"/>
       <c r="BE11"/>
       <c r="BF11"/>
       <c r="BG11"/>
-      <c r="BH11" s="3" t="inlineStr">
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
+      <c r="BK11" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI11" s="3" t="inlineStr">
+      <c r="BL11" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ11" s="3" t="inlineStr">
+      <c r="BM11" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="BK11"/>
-      <c r="BL11" s="3" t="inlineStr">
+      <c r="BN11"/>
+      <c r="BO11" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM11" s="3" t="inlineStr">
+      <c r="BP11" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="BN11" s="3" t="inlineStr">
+      <c r="BQ11" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="BO11" s="4" t="n">
+      <c r="BR11" s="4" t="n">
         <v>14839.0</v>
       </c>
-      <c r="BP11" s="3" t="inlineStr">
+      <c r="BS11" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ11" s="3" t="inlineStr">
+      <c r="BT11" s="3" t="inlineStr">
         <is>
           <t>100 MARKET ST</t>
         </is>
       </c>
-      <c r="BR11" s="3" t="inlineStr">
+      <c r="BU11" s="3" t="inlineStr">
         <is>
           <t>APT 3G</t>
         </is>
       </c>
-      <c r="BS11" s="3" t="inlineStr">
+      <c r="BV11" s="3" t="inlineStr">
         <is>
           <t>CAMP HILL</t>
         </is>
       </c>
-      <c r="BT11" s="3" t="inlineStr">
+      <c r="BW11" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU11" s="3" t="inlineStr">
+      <c r="BX11" s="3" t="inlineStr">
         <is>
           <t>17011</t>
         </is>
       </c>
-      <c r="BV11" s="3" t="inlineStr">
+      <c r="BY11" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW11" s="3" t="inlineStr">
+      <c r="BZ11" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX11" s="3" t="inlineStr">
+      <c r="CA11" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY11" s="3" t="inlineStr">
+      <c r="CB11" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ11"/>
-      <c r="CA11"/>
-      <c r="CB11"/>
       <c r="CC11"/>
       <c r="CD11"/>
       <c r="CE11"/>
@@ -7681,32 +7835,32 @@
       <c r="IZ11"/>
       <c r="JA11"/>
       <c r="JB11"/>
-      <c r="JC11" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD11" s="3" t="inlineStr">
-        <is>
-          <t>VIS</t>
-        </is>
-      </c>
+      <c r="JC11"/>
+      <c r="JD11"/>
       <c r="JE11"/>
       <c r="JF11"/>
       <c r="JG11"/>
       <c r="JH11" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI11" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI11" s="3" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
       </c>
       <c r="JJ11"/>
       <c r="JK11"/>
       <c r="JL11"/>
-      <c r="JM11"/>
-      <c r="JN11"/>
+      <c r="JM11" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN11" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO11"/>
       <c r="JP11"/>
       <c r="JQ11"/>
@@ -7853,11 +8007,22 @@
       <c r="PB11"/>
       <c r="PC11"/>
       <c r="PD11"/>
+      <c r="PE11"/>
+      <c r="PF11"/>
+      <c r="PG11"/>
+      <c r="PH11"/>
+      <c r="PI11"/>
+      <c r="PJ11"/>
+      <c r="PK11"/>
+      <c r="PL11"/>
+      <c r="PM11"/>
+      <c r="PN11"/>
+      <c r="PO11"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fef9</t>
+          <t>6976904ee9a75feb64855213</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -7992,364 +8157,396 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="AG12" s="3" t="inlineStr">
+      <c r="AI12" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH12" s="3" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="AI12" s="3" t="inlineStr">
+      <c r="AJ12" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AJ12"/>
-      <c r="AK12"/>
-      <c r="AL12" s="3" t="inlineStr">
+      <c r="AL12" s="4" t="n">
+        <v>45659.0</v>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>member1</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
+      <c r="AP12" s="3" t="inlineStr">
         <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
+      <c r="AQ12" s="3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AO12" s="3" t="inlineStr">
+      <c r="AR12" s="3" t="inlineStr">
         <is>
           <t>ClientNumber</t>
         </is>
       </c>
-      <c r="AP12"/>
-      <c r="AQ12"/>
-      <c r="AR12"/>
       <c r="AS12"/>
       <c r="AT12"/>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
-      <c r="AX12" s="3" t="inlineStr">
+      <c r="AX12"/>
+      <c r="AY12"/>
+      <c r="AZ12"/>
+      <c r="BA12" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY12" s="4" t="n">
+      <c r="BB12" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ12"/>
-      <c r="BA12"/>
-      <c r="BB12"/>
       <c r="BC12"/>
       <c r="BD12"/>
       <c r="BE12"/>
       <c r="BF12"/>
       <c r="BG12"/>
-      <c r="BH12" s="3" t="inlineStr">
+      <c r="BH12"/>
+      <c r="BI12"/>
+      <c r="BJ12"/>
+      <c r="BK12" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI12" s="3" t="inlineStr">
+      <c r="BL12" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ12" s="3" t="inlineStr">
+      <c r="BM12" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="BK12"/>
-      <c r="BL12" s="3" t="inlineStr">
+      <c r="BN12"/>
+      <c r="BO12" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM12" s="3" t="inlineStr">
+      <c r="BP12" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN12"/>
-      <c r="BO12" s="4" t="n">
+      <c r="BQ12"/>
+      <c r="BR12" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP12" s="3" t="inlineStr">
+      <c r="BS12" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ12" s="3" t="inlineStr">
+      <c r="BT12" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR12"/>
-      <c r="BS12" s="3" t="inlineStr">
+      <c r="BU12"/>
+      <c r="BV12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT12" s="3" t="inlineStr">
+      <c r="BW12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU12" s="3" t="inlineStr">
+      <c r="BX12" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV12" s="3" t="inlineStr">
+      <c r="BY12" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW12" s="3" t="inlineStr">
+      <c r="BZ12" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX12" s="3" t="inlineStr">
+      <c r="CA12" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY12" s="3" t="inlineStr">
+      <c r="CB12" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ12" s="3" t="inlineStr">
+      <c r="CC12" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="CA12" s="3" t="inlineStr">
+      <c r="CD12" s="3" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="CE12" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CF12"/>
+      <c r="CG12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CH12" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="CI12" s="3" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="CJ12" s="3" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="CK12" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="CL12" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CM12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CN12" s="1" t="n">
+        <v>425.25</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="CP12" s="3" t="inlineStr">
+        <is>
+          <t>LocCode</t>
+        </is>
+      </c>
+      <c r="CQ12" s="3" t="inlineStr">
+        <is>
+          <t>SalaryGrade</t>
+        </is>
+      </c>
+      <c r="CR12" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="CS12" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>210.0</v>
+      </c>
+      <c r="CU12" s="3" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="CV12" s="3" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="CW12"/>
+      <c r="CX12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY12" s="3" t="inlineStr">
+        <is>
+          <t>202443309</t>
+        </is>
+      </c>
+      <c r="CZ12" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="DA12" s="3" t="inlineStr">
+        <is>
+          <t>JOE</t>
+        </is>
+      </c>
+      <c r="DB12"/>
+      <c r="DC12" s="4" t="n">
+        <v>25733.0</v>
+      </c>
+      <c r="DD12" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="DE12" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="DF12" s="3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CB12" s="3" t="inlineStr">
+      <c r="DG12" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="CC12" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="CD12" s="3" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="CE12" s="3" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="CF12" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="CG12" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="CH12" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="CI12" s="1" t="n">
-        <v>425.25</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="CK12" s="3" t="inlineStr">
-        <is>
-          <t>LocCode</t>
-        </is>
-      </c>
-      <c r="CL12" s="3" t="inlineStr">
-        <is>
-          <t>SalaryGrade</t>
-        </is>
-      </c>
-      <c r="CM12" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CN12" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="CP12"/>
-      <c r="CQ12"/>
-      <c r="CR12"/>
-      <c r="CS12"/>
-      <c r="CT12" s="3" t="inlineStr">
-        <is>
-          <t>202443309</t>
-        </is>
-      </c>
-      <c r="CU12" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="CV12" s="3" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="CW12"/>
-      <c r="CX12" s="4" t="n">
-        <v>25733.0</v>
-      </c>
-      <c r="CY12" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CZ12" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="DA12" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DB12" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="DC12" s="3" t="inlineStr">
+      <c r="DH12" s="3" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="DD12" s="1" t="n">
+      <c r="DI12" s="1" t="n">
         <v>100.0</v>
       </c>
-      <c r="DE12"/>
-      <c r="DF12"/>
-      <c r="DG12"/>
-      <c r="DH12"/>
-      <c r="DI12"/>
       <c r="DJ12"/>
       <c r="DK12"/>
       <c r="DL12"/>
-      <c r="DM12" s="3" t="inlineStr">
+      <c r="DM12"/>
+      <c r="DN12"/>
+      <c r="DO12"/>
+      <c r="DP12"/>
+      <c r="DQ12"/>
+      <c r="DR12" s="3" t="inlineStr">
         <is>
           <t>9715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="DN12"/>
-      <c r="DO12" s="3" t="inlineStr">
+      <c r="DS12"/>
+      <c r="DT12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="DP12" s="3" t="inlineStr">
+      <c r="DU12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="DQ12" s="3" t="inlineStr">
+      <c r="DV12" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="DR12" s="3" t="inlineStr">
+      <c r="DW12" s="3" t="inlineStr">
         <is>
           <t>emp1ID</t>
         </is>
       </c>
-      <c r="DS12" s="3" t="inlineStr">
+      <c r="DX12" s="3" t="inlineStr">
         <is>
           <t>EMPLOYER1</t>
         </is>
       </c>
-      <c r="DT12" s="3" t="inlineStr">
+      <c r="DY12" s="3" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="DU12" s="3" t="inlineStr">
+      <c r="DZ12" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="DV12" s="3" t="inlineStr">
+      <c r="EA12" s="3" t="inlineStr">
         <is>
           <t>9715 EMPLOYER1 AVENUE</t>
         </is>
       </c>
-      <c r="DW12"/>
-      <c r="DX12" s="3" t="inlineStr">
+      <c r="EB12"/>
+      <c r="EC12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="DY12" s="3" t="inlineStr">
+      <c r="ED12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="DZ12" s="3" t="inlineStr">
+      <c r="EE12" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="EA12" s="3" t="inlineStr">
+      <c r="EF12" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="EB12" s="3" t="inlineStr">
+      <c r="EG12" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="EC12" s="3" t="inlineStr">
+      <c r="EH12" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="ED12" s="3" t="inlineStr">
+      <c r="EI12" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="EE12"/>
-      <c r="EF12"/>
-      <c r="EG12"/>
-      <c r="EH12"/>
-      <c r="EI12"/>
       <c r="EJ12"/>
       <c r="EK12"/>
       <c r="EL12"/>
@@ -8359,195 +8556,195 @@
       <c r="EP12"/>
       <c r="EQ12"/>
       <c r="ER12"/>
-      <c r="ES12" s="3" t="inlineStr">
+      <c r="ES12"/>
+      <c r="ET12"/>
+      <c r="EU12"/>
+      <c r="EV12"/>
+      <c r="EW12"/>
+      <c r="EX12" s="3" t="inlineStr">
         <is>
           <t>School1</t>
         </is>
       </c>
-      <c r="ET12" s="3" t="inlineStr">
+      <c r="EY12" s="3" t="inlineStr">
         <is>
           <t>9715 SCHOOL AVENUE</t>
         </is>
       </c>
-      <c r="EU12"/>
-      <c r="EV12" s="3" t="inlineStr">
+      <c r="EZ12"/>
+      <c r="FA12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="EW12" s="3" t="inlineStr">
+      <c r="FB12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="EX12" s="3" t="inlineStr">
+      <c r="FC12" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="EY12" s="3" t="inlineStr">
+      <c r="FD12" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="EZ12" s="3" t="inlineStr">
+      <c r="FE12" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="FA12" s="3" t="inlineStr">
+      <c r="FF12" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="FB12" s="3" t="inlineStr">
+      <c r="FG12" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="FC12"/>
-      <c r="FD12"/>
-      <c r="FE12"/>
-      <c r="FF12"/>
-      <c r="FG12"/>
       <c r="FH12"/>
       <c r="FI12"/>
       <c r="FJ12"/>
       <c r="FK12"/>
       <c r="FL12"/>
       <c r="FM12"/>
-      <c r="FN12" s="3" t="inlineStr">
+      <c r="FN12"/>
+      <c r="FO12"/>
+      <c r="FP12"/>
+      <c r="FQ12"/>
+      <c r="FR12"/>
+      <c r="FS12" s="3" t="inlineStr">
         <is>
           <t>custodialParentID</t>
         </is>
       </c>
-      <c r="FO12" s="3" t="inlineStr">
+      <c r="FT12" s="3" t="inlineStr">
         <is>
           <t>Custodial</t>
         </is>
       </c>
-      <c r="FP12" s="3" t="inlineStr">
+      <c r="FU12" s="3" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="FQ12" s="3" t="inlineStr">
+      <c r="FV12" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="FR12" s="3" t="inlineStr">
+      <c r="FW12" s="3" t="inlineStr">
         <is>
           <t>9715 CUSTODIAL AVENUE</t>
         </is>
       </c>
-      <c r="FS12"/>
-      <c r="FT12" s="3" t="inlineStr">
+      <c r="FX12"/>
+      <c r="FY12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="FU12" s="3" t="inlineStr">
+      <c r="FZ12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="FV12" s="3" t="inlineStr">
+      <c r="GA12" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="FW12" s="3" t="inlineStr">
+      <c r="GB12" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="FX12" s="3" t="inlineStr">
+      <c r="GC12" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="FY12" s="3" t="inlineStr">
+      <c r="GD12" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="FZ12" s="3" t="inlineStr">
+      <c r="GE12" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="GA12" s="3" t="inlineStr">
+      <c r="GF12" s="3" t="inlineStr">
         <is>
           <t>RESPONSIBLE_PARTY</t>
         </is>
       </c>
-      <c r="GB12" s="3" t="inlineStr">
+      <c r="GG12" s="3" t="inlineStr">
         <is>
           <t>responsiblePersonID</t>
         </is>
       </c>
-      <c r="GC12" s="3" t="inlineStr">
+      <c r="GH12" s="3" t="inlineStr">
         <is>
           <t>Responsible</t>
         </is>
       </c>
-      <c r="GD12" s="3" t="inlineStr">
+      <c r="GI12" s="3" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="GE12" s="3" t="inlineStr">
+      <c r="GJ12" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="GF12" s="3" t="inlineStr">
+      <c r="GK12" s="3" t="inlineStr">
         <is>
           <t>9715 RESPONSIBLE AVENUE</t>
         </is>
       </c>
-      <c r="GG12"/>
-      <c r="GH12" s="3" t="inlineStr">
+      <c r="GL12"/>
+      <c r="GM12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="GI12" s="3" t="inlineStr">
+      <c r="GN12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="GJ12" s="3" t="inlineStr">
+      <c r="GO12" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="GK12" s="3" t="inlineStr">
+      <c r="GP12" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="GL12" s="3" t="inlineStr">
+      <c r="GQ12" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="GM12" s="3" t="inlineStr">
+      <c r="GR12" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="GN12" s="3" t="inlineStr">
+      <c r="GS12" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="GO12"/>
-      <c r="GP12"/>
-      <c r="GQ12"/>
-      <c r="GR12"/>
-      <c r="GS12"/>
       <c r="GT12"/>
       <c r="GU12"/>
       <c r="GV12"/>
@@ -8571,357 +8768,357 @@
       <c r="HN12"/>
       <c r="HO12"/>
       <c r="HP12"/>
-      <c r="HQ12" s="3" t="inlineStr">
-        <is>
-          <t>DropOff</t>
-        </is>
-      </c>
+      <c r="HQ12"/>
       <c r="HR12"/>
       <c r="HS12"/>
-      <c r="HT12" s="3" t="inlineStr">
-        <is>
-          <t>9715 DROPOFF AVENUE</t>
-        </is>
-      </c>
+      <c r="HT12"/>
       <c r="HU12"/>
       <c r="HV12" s="3" t="inlineStr">
         <is>
+          <t>DropOff</t>
+        </is>
+      </c>
+      <c r="HW12"/>
+      <c r="HX12"/>
+      <c r="HY12" s="3" t="inlineStr">
+        <is>
+          <t>9715 DROPOFF AVENUE</t>
+        </is>
+      </c>
+      <c r="HZ12"/>
+      <c r="IA12" s="3" t="inlineStr">
+        <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="HW12" s="3" t="inlineStr">
+      <c r="IB12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="HX12" s="3" t="inlineStr">
+      <c r="IC12" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="HY12" s="3" t="inlineStr">
+      <c r="ID12" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="HZ12" s="3" t="inlineStr">
+      <c r="IE12" s="3" t="inlineStr">
         <is>
           <t>585</t>
         </is>
       </c>
-      <c r="IA12" s="4" t="n">
+      <c r="IF12" s="4" t="n">
         <v>45748.0</v>
       </c>
-      <c r="IB12" s="4" t="n">
+      <c r="IG12" s="4" t="n">
         <v>45778.0</v>
       </c>
-      <c r="IC12"/>
-      <c r="ID12"/>
-      <c r="IE12"/>
-      <c r="IF12"/>
-      <c r="IG12"/>
       <c r="IH12"/>
       <c r="II12"/>
       <c r="IJ12"/>
-      <c r="IK12" s="3" t="inlineStr">
+      <c r="IK12"/>
+      <c r="IL12"/>
+      <c r="IM12"/>
+      <c r="IN12"/>
+      <c r="IO12"/>
+      <c r="IP12" s="3" t="inlineStr">
         <is>
           <t>SOUTHEASTERN UNION</t>
         </is>
       </c>
-      <c r="IL12" s="3" t="inlineStr">
+      <c r="IQ12" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="IM12" s="3" t="inlineStr">
+      <c r="IR12" s="3" t="inlineStr">
         <is>
           <t>UNION_NUMBER</t>
         </is>
       </c>
-      <c r="IN12" s="3" t="inlineStr">
+      <c r="IS12" s="3" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="IO12" s="4" t="n">
+      <c r="IT12" s="4" t="n">
         <v>45717.0</v>
       </c>
-      <c r="IP12" s="4" t="n">
+      <c r="IU12" s="4" t="n">
         <v>45808.0</v>
       </c>
-      <c r="IQ12" s="3" t="inlineStr">
+      <c r="IV12" s="3" t="inlineStr">
         <is>
           <t>PAYER2</t>
         </is>
       </c>
-      <c r="IR12" s="3" t="inlineStr">
+      <c r="IW12" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="IS12" s="3" t="inlineStr">
+      <c r="IX12" s="3" t="inlineStr">
         <is>
           <t>UNION_NUMBER</t>
         </is>
       </c>
-      <c r="IT12" s="3" t="inlineStr">
+      <c r="IY12" s="3" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="IU12" s="4" t="n">
+      <c r="IZ12" s="4" t="n">
         <v>37987.0</v>
       </c>
-      <c r="IV12"/>
-      <c r="IW12"/>
-      <c r="IX12"/>
-      <c r="IY12"/>
-      <c r="IZ12"/>
       <c r="JA12"/>
       <c r="JB12"/>
-      <c r="JC12" s="3" t="inlineStr">
+      <c r="JC12"/>
+      <c r="JD12"/>
+      <c r="JE12"/>
+      <c r="JF12"/>
+      <c r="JG12"/>
+      <c r="JH12" s="3" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="JD12" s="3" t="inlineStr">
+      <c r="JI12" s="3" t="inlineStr">
         <is>
           <t>HMO</t>
         </is>
       </c>
-      <c r="JE12" s="3" t="inlineStr">
+      <c r="JJ12" s="3" t="inlineStr">
         <is>
           <t>PlanDesc</t>
         </is>
       </c>
-      <c r="JF12" s="3" t="inlineStr">
+      <c r="JK12" s="3" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="JG12" s="3" t="inlineStr">
+      <c r="JL12" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="JH12" s="3" t="inlineStr">
+      <c r="JM12" s="3" t="inlineStr">
         <is>
           <t>348</t>
         </is>
       </c>
-      <c r="JI12" s="4" t="n">
+      <c r="JN12" s="4" t="n">
         <v>35217.0</v>
       </c>
-      <c r="JJ12"/>
-      <c r="JK12"/>
-      <c r="JL12"/>
-      <c r="JM12"/>
-      <c r="JN12"/>
       <c r="JO12"/>
       <c r="JP12"/>
       <c r="JQ12"/>
-      <c r="JR12" s="3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="JS12" s="1" t="n">
-        <v>20.0</v>
-      </c>
+      <c r="JR12"/>
+      <c r="JS12"/>
       <c r="JT12"/>
       <c r="JU12"/>
       <c r="JV12"/>
-      <c r="JW12"/>
-      <c r="JX12" s="3" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="JY12" s="3" t="inlineStr">
-        <is>
-          <t>PolicyNumber</t>
-        </is>
-      </c>
+      <c r="JW12" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="JX12" s="1" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="JY12"/>
       <c r="JZ12"/>
       <c r="KA12"/>
       <c r="KB12"/>
-      <c r="KC12"/>
-      <c r="KD12"/>
+      <c r="KC12" s="3" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
+      <c r="KD12" s="3" t="inlineStr">
+        <is>
+          <t>PolicyNumber</t>
+        </is>
+      </c>
       <c r="KE12"/>
       <c r="KF12"/>
       <c r="KG12"/>
-      <c r="KH12" s="3" t="inlineStr">
+      <c r="KH12"/>
+      <c r="KI12"/>
+      <c r="KJ12"/>
+      <c r="KK12"/>
+      <c r="KL12"/>
+      <c r="KM12" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="KI12" s="3" t="inlineStr">
+      <c r="KN12" s="3" t="inlineStr">
         <is>
           <t>PlanDesc</t>
         </is>
       </c>
-      <c r="KJ12" s="3" t="inlineStr">
+      <c r="KO12" s="3" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="KK12" s="2" t="n">
+      <c r="KP12" s="2" t="n">
         <v>5.0</v>
       </c>
-      <c r="KL12" s="3" t="inlineStr">
+      <c r="KQ12" s="3" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="KM12" s="3" t="inlineStr">
+      <c r="KR12" s="3" t="inlineStr">
         <is>
           <t>PRIMARY_CARE</t>
         </is>
       </c>
-      <c r="KN12" s="3" t="inlineStr">
+      <c r="KS12" s="3" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="KO12" s="3" t="inlineStr">
+      <c r="KT12" s="3" t="inlineStr">
         <is>
           <t>prov1ID</t>
         </is>
       </c>
-      <c r="KP12" s="3" t="inlineStr">
+      <c r="KU12" s="3" t="inlineStr">
         <is>
           <t>BROWN</t>
         </is>
       </c>
-      <c r="KQ12" s="3" t="inlineStr">
+      <c r="KV12" s="3" t="inlineStr">
         <is>
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="KR12"/>
-      <c r="KS12" s="3" t="inlineStr">
+      <c r="KW12"/>
+      <c r="KX12" s="3" t="inlineStr">
         <is>
           <t>2715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="KT12"/>
-      <c r="KU12" s="3" t="inlineStr">
+      <c r="KY12"/>
+      <c r="KZ12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="KV12" s="3" t="inlineStr">
+      <c r="LA12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="KW12" s="3" t="inlineStr">
+      <c r="LB12" s="3" t="inlineStr">
         <is>
           <t>271110000</t>
         </is>
       </c>
-      <c r="KX12" s="3" t="inlineStr">
+      <c r="LC12" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="KY12" s="3" t="inlineStr">
+      <c r="LD12" s="3" t="inlineStr">
         <is>
           <t>2172343334</t>
         </is>
       </c>
-      <c r="KZ12" s="3" t="inlineStr">
+      <c r="LE12" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="LA12" s="3" t="inlineStr">
+      <c r="LF12" s="3" t="inlineStr">
         <is>
           <t>2172341240</t>
         </is>
       </c>
-      <c r="LB12" s="3" t="inlineStr">
+      <c r="LG12" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="LC12" s="4" t="n">
+      <c r="LH12" s="4" t="n">
         <v>45413.0</v>
       </c>
-      <c r="LD12" s="3" t="inlineStr">
+      <c r="LI12" s="3" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="LE12" s="3" t="inlineStr">
+      <c r="LJ12" s="3" t="inlineStr">
         <is>
           <t>MANAGED_CARE</t>
         </is>
       </c>
-      <c r="LF12" s="3" t="inlineStr">
+      <c r="LK12" s="3" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="LG12" s="3" t="inlineStr">
+      <c r="LL12" s="3" t="inlineStr">
         <is>
           <t>943766</t>
         </is>
       </c>
-      <c r="LH12" s="3" t="inlineStr">
+      <c r="LM12" s="3" t="inlineStr">
         <is>
           <t>BROWN</t>
         </is>
       </c>
-      <c r="LI12" s="3" t="inlineStr">
+      <c r="LN12" s="3" t="inlineStr">
         <is>
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="LJ12"/>
-      <c r="LK12" s="3" t="inlineStr">
+      <c r="LO12"/>
+      <c r="LP12" s="3" t="inlineStr">
         <is>
           <t>2715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="LL12"/>
-      <c r="LM12" s="3" t="inlineStr">
+      <c r="LQ12"/>
+      <c r="LR12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="LN12" s="3" t="inlineStr">
+      <c r="LS12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="LO12" s="3" t="inlineStr">
+      <c r="LT12" s="3" t="inlineStr">
         <is>
           <t>271110000</t>
         </is>
       </c>
-      <c r="LP12"/>
-      <c r="LQ12"/>
-      <c r="LR12"/>
-      <c r="LS12"/>
-      <c r="LT12" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="LU12" s="4" t="n">
-        <v>45047.0</v>
-      </c>
-      <c r="LV12" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+      <c r="LU12"/>
+      <c r="LV12"/>
       <c r="LW12"/>
       <c r="LX12"/>
-      <c r="LY12"/>
-      <c r="LZ12"/>
-      <c r="MA12"/>
+      <c r="LY12" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="LZ12" s="4" t="n">
+        <v>45047.0</v>
+      </c>
+      <c r="MA12" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
       <c r="MB12"/>
       <c r="MC12"/>
       <c r="MD12"/>
@@ -8935,116 +9132,124 @@
       <c r="ML12"/>
       <c r="MM12"/>
       <c r="MN12"/>
-      <c r="MO12" s="3" t="inlineStr">
+      <c r="MO12"/>
+      <c r="MP12"/>
+      <c r="MQ12"/>
+      <c r="MR12"/>
+      <c r="MS12"/>
+      <c r="MT12" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="MP12" s="3" t="inlineStr">
+      <c r="MU12" s="3" t="inlineStr">
         <is>
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="MQ12" s="3" t="inlineStr">
+      <c r="MV12" s="3" t="inlineStr">
         <is>
           <t>XYZ123</t>
         </is>
       </c>
-      <c r="MR12" s="3" t="inlineStr">
+      <c r="MW12" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="MS12" s="3" t="inlineStr">
+      <c r="MX12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="MY12" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="MZ12"/>
+      <c r="NA12" s="3" t="inlineStr">
         <is>
           <t>6P</t>
         </is>
       </c>
-      <c r="MT12" s="3" t="inlineStr">
+      <c r="NB12" s="3" t="inlineStr">
         <is>
           <t>COB-GroupNumber</t>
         </is>
       </c>
-      <c r="MU12" s="3" t="inlineStr">
+      <c r="NC12" s="3" t="inlineStr">
         <is>
           <t>SY</t>
         </is>
       </c>
-      <c r="MV12" s="3" t="inlineStr">
+      <c r="ND12" s="3" t="inlineStr">
         <is>
           <t>COB-SSN</t>
         </is>
       </c>
-      <c r="MW12" s="4" t="n">
+      <c r="NE12" s="4" t="n">
         <v>45689.0</v>
       </c>
-      <c r="MX12" s="4" t="n">
+      <c r="NF12" s="4" t="n">
         <v>45716.0</v>
       </c>
-      <c r="MY12" s="3" t="inlineStr">
+      <c r="NG12" s="3" t="inlineStr">
         <is>
           <t>EMPLOYER</t>
         </is>
       </c>
-      <c r="MZ12" s="3" t="inlineStr">
+      <c r="NH12" s="3" t="inlineStr">
         <is>
           <t>COB-EmployerId</t>
         </is>
       </c>
-      <c r="NA12" s="3" t="inlineStr">
+      <c r="NI12" s="3" t="inlineStr">
         <is>
           <t>COB-Employer</t>
         </is>
       </c>
-      <c r="NB12" s="3" t="inlineStr">
+      <c r="NJ12" s="3" t="inlineStr">
         <is>
           <t>9715 RESPONSIBLE AVENUE</t>
         </is>
       </c>
-      <c r="NC12"/>
-      <c r="ND12" s="3" t="inlineStr">
+      <c r="NK12"/>
+      <c r="NL12" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="NE12" s="3" t="inlineStr">
+      <c r="NM12" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="NF12" s="3" t="inlineStr">
+      <c r="NN12" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="NG12" s="3" t="inlineStr">
+      <c r="NO12" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="NH12" s="3" t="inlineStr">
+      <c r="NP12" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="NI12" s="3" t="inlineStr">
+      <c r="NQ12" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="NJ12" s="3" t="inlineStr">
+      <c r="NR12" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="NK12"/>
-      <c r="NL12"/>
-      <c r="NM12"/>
-      <c r="NN12"/>
-      <c r="NO12"/>
-      <c r="NP12"/>
-      <c r="NQ12"/>
-      <c r="NR12"/>
       <c r="NS12"/>
       <c r="NT12"/>
       <c r="NU12"/>
@@ -9083,11 +9288,22 @@
       <c r="PB12"/>
       <c r="PC12"/>
       <c r="PD12"/>
+      <c r="PE12"/>
+      <c r="PF12"/>
+      <c r="PG12"/>
+      <c r="PH12"/>
+      <c r="PI12"/>
+      <c r="PJ12"/>
+      <c r="PK12"/>
+      <c r="PL12"/>
+      <c r="PM12"/>
+      <c r="PN12"/>
+      <c r="PO12"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fef9</t>
+          <t>6976904ee9a75feb64855213</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9222,364 +9438,396 @@
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="AG13" s="3" t="inlineStr">
+      <c r="AI13" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH13" s="3" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="AI13" s="3" t="inlineStr">
+      <c r="AJ13" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AJ13"/>
-      <c r="AK13"/>
-      <c r="AL13" s="3" t="inlineStr">
+      <c r="AL13" s="4" t="n">
+        <v>45659.0</v>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="AN13" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>member1</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
+      <c r="AP13" s="3" t="inlineStr">
         <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
+      <c r="AQ13" s="3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AO13" s="3" t="inlineStr">
+      <c r="AR13" s="3" t="inlineStr">
         <is>
           <t>ClientNumber</t>
         </is>
       </c>
-      <c r="AP13"/>
-      <c r="AQ13"/>
-      <c r="AR13"/>
       <c r="AS13"/>
       <c r="AT13"/>
       <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13"/>
-      <c r="AX13" s="3" t="inlineStr">
+      <c r="AX13"/>
+      <c r="AY13"/>
+      <c r="AZ13"/>
+      <c r="BA13" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY13" s="4" t="n">
+      <c r="BB13" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ13"/>
-      <c r="BA13"/>
-      <c r="BB13"/>
       <c r="BC13"/>
       <c r="BD13"/>
       <c r="BE13"/>
       <c r="BF13"/>
       <c r="BG13"/>
-      <c r="BH13" s="3" t="inlineStr">
+      <c r="BH13"/>
+      <c r="BI13"/>
+      <c r="BJ13"/>
+      <c r="BK13" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI13" s="3" t="inlineStr">
+      <c r="BL13" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ13" s="3" t="inlineStr">
+      <c r="BM13" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="BK13"/>
-      <c r="BL13" s="3" t="inlineStr">
+      <c r="BN13"/>
+      <c r="BO13" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM13" s="3" t="inlineStr">
+      <c r="BP13" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN13"/>
-      <c r="BO13" s="4" t="n">
+      <c r="BQ13"/>
+      <c r="BR13" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP13" s="3" t="inlineStr">
+      <c r="BS13" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ13" s="3" t="inlineStr">
+      <c r="BT13" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR13"/>
-      <c r="BS13" s="3" t="inlineStr">
+      <c r="BU13"/>
+      <c r="BV13" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT13" s="3" t="inlineStr">
+      <c r="BW13" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU13" s="3" t="inlineStr">
+      <c r="BX13" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV13" s="3" t="inlineStr">
+      <c r="BY13" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW13" s="3" t="inlineStr">
+      <c r="BZ13" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX13" s="3" t="inlineStr">
+      <c r="CA13" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY13" s="3" t="inlineStr">
+      <c r="CB13" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ13" s="3" t="inlineStr">
+      <c r="CC13" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="CA13" s="3" t="inlineStr">
+      <c r="CD13" s="3" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="CE13" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CF13"/>
+      <c r="CG13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CH13" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="CI13" s="3" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="CJ13" s="3" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="CK13" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="CL13" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CM13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CN13" s="1" t="n">
+        <v>425.25</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="CP13" s="3" t="inlineStr">
+        <is>
+          <t>LocCode</t>
+        </is>
+      </c>
+      <c r="CQ13" s="3" t="inlineStr">
+        <is>
+          <t>SalaryGrade</t>
+        </is>
+      </c>
+      <c r="CR13" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="CS13" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>210.0</v>
+      </c>
+      <c r="CU13" s="3" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="CV13" s="3" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="CW13"/>
+      <c r="CX13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY13" s="3" t="inlineStr">
+        <is>
+          <t>202443309</t>
+        </is>
+      </c>
+      <c r="CZ13" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="DA13" s="3" t="inlineStr">
+        <is>
+          <t>JOE</t>
+        </is>
+      </c>
+      <c r="DB13"/>
+      <c r="DC13" s="4" t="n">
+        <v>25733.0</v>
+      </c>
+      <c r="DD13" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="DE13" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="DF13" s="3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CB13" s="3" t="inlineStr">
+      <c r="DG13" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="CC13" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="CD13" s="3" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="CE13" s="3" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="CF13" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="CG13" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="CH13" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="CI13" s="1" t="n">
-        <v>425.25</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="CK13" s="3" t="inlineStr">
-        <is>
-          <t>LocCode</t>
-        </is>
-      </c>
-      <c r="CL13" s="3" t="inlineStr">
-        <is>
-          <t>SalaryGrade</t>
-        </is>
-      </c>
-      <c r="CM13" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CN13" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="CP13"/>
-      <c r="CQ13"/>
-      <c r="CR13"/>
-      <c r="CS13"/>
-      <c r="CT13" s="3" t="inlineStr">
-        <is>
-          <t>202443309</t>
-        </is>
-      </c>
-      <c r="CU13" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="CV13" s="3" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="CW13"/>
-      <c r="CX13" s="4" t="n">
-        <v>25733.0</v>
-      </c>
-      <c r="CY13" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CZ13" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="DA13" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DB13" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="DC13" s="3" t="inlineStr">
+      <c r="DH13" s="3" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="DD13" s="1" t="n">
+      <c r="DI13" s="1" t="n">
         <v>100.0</v>
       </c>
-      <c r="DE13"/>
-      <c r="DF13"/>
-      <c r="DG13"/>
-      <c r="DH13"/>
-      <c r="DI13"/>
       <c r="DJ13"/>
       <c r="DK13"/>
       <c r="DL13"/>
-      <c r="DM13" s="3" t="inlineStr">
+      <c r="DM13"/>
+      <c r="DN13"/>
+      <c r="DO13"/>
+      <c r="DP13"/>
+      <c r="DQ13"/>
+      <c r="DR13" s="3" t="inlineStr">
         <is>
           <t>9715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="DN13"/>
-      <c r="DO13" s="3" t="inlineStr">
+      <c r="DS13"/>
+      <c r="DT13" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="DP13" s="3" t="inlineStr">
+      <c r="DU13" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="DQ13" s="3" t="inlineStr">
+      <c r="DV13" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="DR13" s="3" t="inlineStr">
+      <c r="DW13" s="3" t="inlineStr">
         <is>
           <t>emp1ID</t>
         </is>
       </c>
-      <c r="DS13" s="3" t="inlineStr">
+      <c r="DX13" s="3" t="inlineStr">
         <is>
           <t>EMPLOYER1</t>
         </is>
       </c>
-      <c r="DT13" s="3" t="inlineStr">
+      <c r="DY13" s="3" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="DU13" s="3" t="inlineStr">
+      <c r="DZ13" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="DV13" s="3" t="inlineStr">
+      <c r="EA13" s="3" t="inlineStr">
         <is>
           <t>9715 EMPLOYER1 AVENUE</t>
         </is>
       </c>
-      <c r="DW13"/>
-      <c r="DX13" s="3" t="inlineStr">
+      <c r="EB13"/>
+      <c r="EC13" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="DY13" s="3" t="inlineStr">
+      <c r="ED13" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="DZ13" s="3" t="inlineStr">
+      <c r="EE13" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="EA13" s="3" t="inlineStr">
+      <c r="EF13" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="EB13" s="3" t="inlineStr">
+      <c r="EG13" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="EC13" s="3" t="inlineStr">
+      <c r="EH13" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="ED13" s="3" t="inlineStr">
+      <c r="EI13" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="EE13"/>
-      <c r="EF13"/>
-      <c r="EG13"/>
-      <c r="EH13"/>
-      <c r="EI13"/>
       <c r="EJ13"/>
       <c r="EK13"/>
       <c r="EL13"/>
@@ -9589,195 +9837,195 @@
       <c r="EP13"/>
       <c r="EQ13"/>
       <c r="ER13"/>
-      <c r="ES13" s="3" t="inlineStr">
+      <c r="ES13"/>
+      <c r="ET13"/>
+      <c r="EU13"/>
+      <c r="EV13"/>
+      <c r="EW13"/>
+      <c r="EX13" s="3" t="inlineStr">
         <is>
           <t>School1</t>
         </is>
       </c>
-      <c r="ET13" s="3" t="inlineStr">
+      <c r="EY13" s="3" t="inlineStr">
         <is>
           <t>9715 SCHOOL AVENUE</t>
         </is>
       </c>
-      <c r="EU13"/>
-      <c r="EV13" s="3" t="inlineStr">
+      <c r="EZ13"/>
+      <c r="FA13" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="EW13" s="3" t="inlineStr">
+      <c r="FB13" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="EX13" s="3" t="inlineStr">
+      <c r="FC13" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="EY13" s="3" t="inlineStr">
+      <c r="FD13" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="EZ13" s="3" t="inlineStr">
+      <c r="FE13" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="FA13" s="3" t="inlineStr">
+      <c r="FF13" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="FB13" s="3" t="inlineStr">
+      <c r="FG13" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="FC13"/>
-      <c r="FD13"/>
-      <c r="FE13"/>
-      <c r="FF13"/>
-      <c r="FG13"/>
       <c r="FH13"/>
       <c r="FI13"/>
       <c r="FJ13"/>
       <c r="FK13"/>
       <c r="FL13"/>
       <c r="FM13"/>
-      <c r="FN13" s="3" t="inlineStr">
+      <c r="FN13"/>
+      <c r="FO13"/>
+      <c r="FP13"/>
+      <c r="FQ13"/>
+      <c r="FR13"/>
+      <c r="FS13" s="3" t="inlineStr">
         <is>
           <t>custodialParentID</t>
         </is>
       </c>
-      <c r="FO13" s="3" t="inlineStr">
+      <c r="FT13" s="3" t="inlineStr">
         <is>
           <t>Custodial</t>
         </is>
       </c>
-      <c r="FP13" s="3" t="inlineStr">
+      <c r="FU13" s="3" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="FQ13" s="3" t="inlineStr">
+      <c r="FV13" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="FR13" s="3" t="inlineStr">
+      <c r="FW13" s="3" t="inlineStr">
         <is>
           <t>9715 CUSTODIAL AVENUE</t>
         </is>
       </c>
-      <c r="FS13"/>
-      <c r="FT13" s="3" t="inlineStr">
+      <c r="FX13"/>
+      <c r="FY13" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="FU13" s="3" t="inlineStr">
+      <c r="FZ13" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="FV13" s="3" t="inlineStr">
+      <c r="GA13" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="FW13" s="3" t="inlineStr">
+      <c r="GB13" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="FX13" s="3" t="inlineStr">
+      <c r="GC13" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="FY13" s="3" t="inlineStr">
+      <c r="GD13" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="FZ13" s="3" t="inlineStr">
+      <c r="GE13" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="GA13" s="3" t="inlineStr">
+      <c r="GF13" s="3" t="inlineStr">
         <is>
           <t>RESPONSIBLE_PARTY</t>
         </is>
       </c>
-      <c r="GB13" s="3" t="inlineStr">
+      <c r="GG13" s="3" t="inlineStr">
         <is>
           <t>responsiblePersonID</t>
         </is>
       </c>
-      <c r="GC13" s="3" t="inlineStr">
+      <c r="GH13" s="3" t="inlineStr">
         <is>
           <t>Responsible</t>
         </is>
       </c>
-      <c r="GD13" s="3" t="inlineStr">
+      <c r="GI13" s="3" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="GE13" s="3" t="inlineStr">
+      <c r="GJ13" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="GF13" s="3" t="inlineStr">
+      <c r="GK13" s="3" t="inlineStr">
         <is>
           <t>9715 RESPONSIBLE AVENUE</t>
         </is>
       </c>
-      <c r="GG13"/>
-      <c r="GH13" s="3" t="inlineStr">
+      <c r="GL13"/>
+      <c r="GM13" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="GI13" s="3" t="inlineStr">
+      <c r="GN13" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="GJ13" s="3" t="inlineStr">
+      <c r="GO13" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="GK13" s="3" t="inlineStr">
+      <c r="GP13" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="GL13" s="3" t="inlineStr">
+      <c r="GQ13" s="3" t="inlineStr">
         <is>
           <t>9172343334</t>
         </is>
       </c>
-      <c r="GM13" s="3" t="inlineStr">
+      <c r="GR13" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="GN13" s="3" t="inlineStr">
+      <c r="GS13" s="3" t="inlineStr">
         <is>
           <t>9172341240</t>
         </is>
       </c>
-      <c r="GO13"/>
-      <c r="GP13"/>
-      <c r="GQ13"/>
-      <c r="GR13"/>
-      <c r="GS13"/>
       <c r="GT13"/>
       <c r="GU13"/>
       <c r="GV13"/>
@@ -9801,195 +10049,195 @@
       <c r="HN13"/>
       <c r="HO13"/>
       <c r="HP13"/>
-      <c r="HQ13" s="3" t="inlineStr">
-        <is>
-          <t>DropOff</t>
-        </is>
-      </c>
+      <c r="HQ13"/>
       <c r="HR13"/>
       <c r="HS13"/>
-      <c r="HT13" s="3" t="inlineStr">
-        <is>
-          <t>9715 DROPOFF AVENUE</t>
-        </is>
-      </c>
+      <c r="HT13"/>
       <c r="HU13"/>
       <c r="HV13" s="3" t="inlineStr">
         <is>
+          <t>DropOff</t>
+        </is>
+      </c>
+      <c r="HW13"/>
+      <c r="HX13"/>
+      <c r="HY13" s="3" t="inlineStr">
+        <is>
+          <t>9715 DROPOFF AVENUE</t>
+        </is>
+      </c>
+      <c r="HZ13"/>
+      <c r="IA13" s="3" t="inlineStr">
+        <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="HW13" s="3" t="inlineStr">
+      <c r="IB13" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="HX13" s="3" t="inlineStr">
+      <c r="IC13" s="3" t="inlineStr">
         <is>
           <t>971110000</t>
         </is>
       </c>
-      <c r="HY13" s="3" t="inlineStr">
+      <c r="ID13" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="HZ13" s="3" t="inlineStr">
+      <c r="IE13" s="3" t="inlineStr">
         <is>
           <t>585</t>
         </is>
       </c>
-      <c r="IA13" s="4" t="n">
+      <c r="IF13" s="4" t="n">
         <v>45748.0</v>
       </c>
-      <c r="IB13" s="4" t="n">
+      <c r="IG13" s="4" t="n">
         <v>45778.0</v>
       </c>
-      <c r="IC13"/>
-      <c r="ID13"/>
-      <c r="IE13"/>
-      <c r="IF13"/>
-      <c r="IG13"/>
       <c r="IH13"/>
       <c r="II13"/>
       <c r="IJ13"/>
-      <c r="IK13" s="3" t="inlineStr">
+      <c r="IK13"/>
+      <c r="IL13"/>
+      <c r="IM13"/>
+      <c r="IN13"/>
+      <c r="IO13"/>
+      <c r="IP13" s="3" t="inlineStr">
         <is>
           <t>SOUTHEASTERN UNION</t>
         </is>
       </c>
-      <c r="IL13" s="3" t="inlineStr">
+      <c r="IQ13" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="IM13" s="3" t="inlineStr">
+      <c r="IR13" s="3" t="inlineStr">
         <is>
           <t>UNION_NUMBER</t>
         </is>
       </c>
-      <c r="IN13" s="3" t="inlineStr">
+      <c r="IS13" s="3" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="IO13" s="4" t="n">
+      <c r="IT13" s="4" t="n">
         <v>45717.0</v>
       </c>
-      <c r="IP13" s="4" t="n">
+      <c r="IU13" s="4" t="n">
         <v>45808.0</v>
       </c>
-      <c r="IQ13" s="3" t="inlineStr">
+      <c r="IV13" s="3" t="inlineStr">
         <is>
           <t>PAYER2</t>
         </is>
       </c>
-      <c r="IR13" s="3" t="inlineStr">
+      <c r="IW13" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="IS13" s="3" t="inlineStr">
+      <c r="IX13" s="3" t="inlineStr">
         <is>
           <t>UNION_NUMBER</t>
         </is>
       </c>
-      <c r="IT13" s="3" t="inlineStr">
+      <c r="IY13" s="3" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="IU13" s="4" t="n">
+      <c r="IZ13" s="4" t="n">
         <v>37987.0</v>
       </c>
-      <c r="IV13"/>
-      <c r="IW13"/>
-      <c r="IX13"/>
-      <c r="IY13"/>
-      <c r="IZ13"/>
       <c r="JA13"/>
       <c r="JB13"/>
-      <c r="JC13" s="3" t="inlineStr">
+      <c r="JC13"/>
+      <c r="JD13"/>
+      <c r="JE13"/>
+      <c r="JF13"/>
+      <c r="JG13"/>
+      <c r="JH13" s="3" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="JD13" s="3" t="inlineStr">
+      <c r="JI13" s="3" t="inlineStr">
         <is>
           <t>EPO</t>
         </is>
       </c>
-      <c r="JE13" s="3" t="inlineStr">
+      <c r="JJ13" s="3" t="inlineStr">
         <is>
           <t>PlanDesc2</t>
         </is>
       </c>
-      <c r="JF13" s="3" t="inlineStr">
+      <c r="JK13" s="3" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="JG13" s="3" t="inlineStr">
+      <c r="JL13" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="JH13" s="3" t="inlineStr">
+      <c r="JM13" s="3" t="inlineStr">
         <is>
           <t>348</t>
         </is>
       </c>
-      <c r="JI13" s="4" t="n">
+      <c r="JN13" s="4" t="n">
         <v>45778.0</v>
       </c>
-      <c r="JJ13"/>
-      <c r="JK13"/>
-      <c r="JL13"/>
-      <c r="JM13"/>
-      <c r="JN13"/>
       <c r="JO13"/>
       <c r="JP13"/>
       <c r="JQ13"/>
-      <c r="JR13" s="3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="JS13" s="1" t="n">
-        <v>20.0</v>
-      </c>
+      <c r="JR13"/>
+      <c r="JS13"/>
       <c r="JT13"/>
       <c r="JU13"/>
       <c r="JV13"/>
-      <c r="JW13"/>
-      <c r="JX13" s="3" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="JY13" s="3" t="inlineStr">
-        <is>
-          <t>PolicyNumber2</t>
-        </is>
-      </c>
+      <c r="JW13" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="JX13" s="1" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="JY13"/>
       <c r="JZ13"/>
       <c r="KA13"/>
       <c r="KB13"/>
-      <c r="KC13"/>
-      <c r="KD13"/>
+      <c r="KC13" s="3" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
+      <c r="KD13" s="3" t="inlineStr">
+        <is>
+          <t>PolicyNumber2</t>
+        </is>
+      </c>
       <c r="KE13"/>
       <c r="KF13"/>
       <c r="KG13"/>
-      <c r="KH13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="KH13"/>
       <c r="KI13"/>
       <c r="KJ13"/>
       <c r="KK13"/>
       <c r="KL13"/>
-      <c r="KM13"/>
+      <c r="KM13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="KN13"/>
       <c r="KO13"/>
       <c r="KP13"/>
@@ -10111,11 +10359,22 @@
       <c r="PB13"/>
       <c r="PC13"/>
       <c r="PD13"/>
+      <c r="PE13"/>
+      <c r="PF13"/>
+      <c r="PG13"/>
+      <c r="PH13"/>
+      <c r="PI13"/>
+      <c r="PJ13"/>
+      <c r="PK13"/>
+      <c r="PL13"/>
+      <c r="PM13"/>
+      <c r="PN13"/>
+      <c r="PO13"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fefa</t>
+          <t>6976904ee9a75feb64855214</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -10249,28 +10508,28 @@
         </is>
       </c>
       <c r="AF14"/>
-      <c r="AG14" s="3" t="inlineStr">
+      <c r="AG14"/>
+      <c r="AH14"/>
+      <c r="AI14" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH14"/>
-      <c r="AI14"/>
       <c r="AJ14"/>
       <c r="AK14"/>
-      <c r="AL14" s="3" t="inlineStr">
+      <c r="AL14"/>
+      <c r="AM14"/>
+      <c r="AN14"/>
+      <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>member2</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
+      <c r="AP14" s="3" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="AN14"/>
-      <c r="AO14"/>
-      <c r="AP14"/>
       <c r="AQ14"/>
       <c r="AR14"/>
       <c r="AS14"/>
@@ -10278,101 +10537,101 @@
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
-      <c r="AX14" s="3" t="inlineStr">
+      <c r="AX14"/>
+      <c r="AY14"/>
+      <c r="AZ14"/>
+      <c r="BA14" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY14" s="4" t="n">
+      <c r="BB14" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ14"/>
-      <c r="BA14"/>
-      <c r="BB14"/>
       <c r="BC14"/>
       <c r="BD14"/>
       <c r="BE14"/>
       <c r="BF14"/>
       <c r="BG14"/>
-      <c r="BH14" s="3" t="inlineStr">
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
+      <c r="BK14" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI14" s="3" t="inlineStr">
+      <c r="BL14" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ14" s="3" t="inlineStr">
+      <c r="BM14" s="3" t="inlineStr">
         <is>
           <t>202443309</t>
         </is>
       </c>
-      <c r="BK14"/>
-      <c r="BL14" s="3" t="inlineStr">
+      <c r="BN14"/>
+      <c r="BO14" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM14" s="3" t="inlineStr">
+      <c r="BP14" s="3" t="inlineStr">
         <is>
           <t>Jane</t>
         </is>
       </c>
-      <c r="BN14"/>
-      <c r="BO14" s="4" t="n">
+      <c r="BQ14"/>
+      <c r="BR14" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP14" s="3" t="inlineStr">
+      <c r="BS14" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ14" s="3" t="inlineStr">
+      <c r="BT14" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR14"/>
-      <c r="BS14" s="3" t="inlineStr">
+      <c r="BU14"/>
+      <c r="BV14" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT14" s="3" t="inlineStr">
+      <c r="BW14" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU14" s="3" t="inlineStr">
+      <c r="BX14" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV14" s="3" t="inlineStr">
+      <c r="BY14" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW14" s="3" t="inlineStr">
+      <c r="BZ14" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX14" s="3" t="inlineStr">
+      <c r="CA14" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY14" s="3" t="inlineStr">
+      <c r="CB14" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ14"/>
-      <c r="CA14"/>
-      <c r="CB14"/>
       <c r="CC14"/>
       <c r="CD14"/>
       <c r="CE14"/>
@@ -10555,32 +10814,32 @@
       <c r="IZ14"/>
       <c r="JA14"/>
       <c r="JB14"/>
-      <c r="JC14" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD14" s="3" t="inlineStr">
-        <is>
-          <t>HMO</t>
-        </is>
-      </c>
+      <c r="JC14"/>
+      <c r="JD14"/>
       <c r="JE14"/>
       <c r="JF14"/>
       <c r="JG14"/>
       <c r="JH14" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI14" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI14" s="3" t="inlineStr">
+        <is>
+          <t>HMO</t>
+        </is>
       </c>
       <c r="JJ14"/>
       <c r="JK14"/>
       <c r="JL14"/>
-      <c r="JM14"/>
-      <c r="JN14"/>
+      <c r="JM14" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN14" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO14"/>
       <c r="JP14"/>
       <c r="JQ14"/>
@@ -10605,59 +10864,59 @@
       <c r="KJ14"/>
       <c r="KK14"/>
       <c r="KL14"/>
-      <c r="KM14" s="3" t="inlineStr">
+      <c r="KM14"/>
+      <c r="KN14"/>
+      <c r="KO14"/>
+      <c r="KP14"/>
+      <c r="KQ14"/>
+      <c r="KR14" s="3" t="inlineStr">
         <is>
           <t>PRIMARY_CARE</t>
         </is>
       </c>
-      <c r="KN14" s="3" t="inlineStr">
+      <c r="KS14" s="3" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="KO14" s="3" t="inlineStr">
+      <c r="KT14" s="3" t="inlineStr">
         <is>
           <t>143766</t>
         </is>
       </c>
-      <c r="KP14" s="3" t="inlineStr">
+      <c r="KU14" s="3" t="inlineStr">
         <is>
           <t>BROWN</t>
         </is>
       </c>
-      <c r="KQ14" s="3" t="inlineStr">
+      <c r="KV14" s="3" t="inlineStr">
         <is>
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="KR14"/>
-      <c r="KS14"/>
-      <c r="KT14"/>
-      <c r="KU14"/>
-      <c r="KV14"/>
       <c r="KW14"/>
       <c r="KX14"/>
       <c r="KY14"/>
       <c r="KZ14"/>
       <c r="LA14"/>
-      <c r="LB14" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="LC14" s="4" t="n">
-        <v>45413.0</v>
-      </c>
-      <c r="LD14" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+      <c r="LB14"/>
+      <c r="LC14"/>
+      <c r="LD14"/>
       <c r="LE14"/>
       <c r="LF14"/>
-      <c r="LG14"/>
-      <c r="LH14"/>
-      <c r="LI14"/>
+      <c r="LG14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="LH14" s="4" t="n">
+        <v>45413.0</v>
+      </c>
+      <c r="LI14" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
       <c r="LJ14"/>
       <c r="LK14"/>
       <c r="LL14"/>
@@ -10757,11 +11016,22 @@
       <c r="PB14"/>
       <c r="PC14"/>
       <c r="PD14"/>
+      <c r="PE14"/>
+      <c r="PF14"/>
+      <c r="PG14"/>
+      <c r="PH14"/>
+      <c r="PI14"/>
+      <c r="PJ14"/>
+      <c r="PK14"/>
+      <c r="PL14"/>
+      <c r="PM14"/>
+      <c r="PN14"/>
+      <c r="PO14"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499fefb</t>
+          <t>6976904ee9a75feb64855215</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -10858,151 +11128,151 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AF15" s="3" t="inlineStr">
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15" s="3" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="AG15" s="3" t="inlineStr">
+      <c r="AI15" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
+      <c r="AJ15" s="3" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="AI15" s="3" t="inlineStr">
+      <c r="AK15" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AJ15"/>
-      <c r="AK15"/>
-      <c r="AL15" s="3" t="inlineStr">
+      <c r="AL15"/>
+      <c r="AM15"/>
+      <c r="AN15"/>
+      <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>member3</t>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
+      <c r="AP15" s="3" t="inlineStr">
         <is>
           <t>group3</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
+      <c r="AQ15" s="3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AO15" s="3" t="inlineStr">
+      <c r="AR15" s="3" t="inlineStr">
         <is>
           <t>ClientNumber3</t>
         </is>
       </c>
-      <c r="AP15"/>
-      <c r="AQ15"/>
-      <c r="AR15"/>
       <c r="AS15"/>
       <c r="AT15"/>
       <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
-      <c r="AX15" s="3" t="inlineStr">
+      <c r="AX15"/>
+      <c r="AY15"/>
+      <c r="AZ15"/>
+      <c r="BA15" s="3" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="AY15" s="4" t="n">
+      <c r="BB15" s="4" t="n">
         <v>35076.0</v>
       </c>
-      <c r="AZ15"/>
-      <c r="BA15"/>
-      <c r="BB15"/>
       <c r="BC15"/>
       <c r="BD15"/>
       <c r="BE15"/>
       <c r="BF15"/>
       <c r="BG15"/>
-      <c r="BH15" s="3" t="inlineStr">
+      <c r="BH15"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
+      <c r="BK15" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI15" s="3" t="inlineStr">
+      <c r="BL15" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ15" s="3" t="inlineStr">
+      <c r="BM15" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="BK15"/>
-      <c r="BL15" s="3" t="inlineStr">
+      <c r="BN15"/>
+      <c r="BO15" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM15" s="3" t="inlineStr">
+      <c r="BP15" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN15"/>
-      <c r="BO15" s="4" t="n">
+      <c r="BQ15"/>
+      <c r="BR15" s="4" t="n">
         <v>25733.0</v>
       </c>
-      <c r="BP15" s="3" t="inlineStr">
+      <c r="BS15" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ15" s="3" t="inlineStr">
+      <c r="BT15" s="3" t="inlineStr">
         <is>
           <t>1715 SOUTHWIND AVENUE</t>
         </is>
       </c>
-      <c r="BR15"/>
-      <c r="BS15" s="3" t="inlineStr">
+      <c r="BU15"/>
+      <c r="BV15" s="3" t="inlineStr">
         <is>
           <t>ANYTOWN</t>
         </is>
       </c>
-      <c r="BT15" s="3" t="inlineStr">
+      <c r="BW15" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BU15" s="3" t="inlineStr">
+      <c r="BX15" s="3" t="inlineStr">
         <is>
           <t>171110000</t>
         </is>
       </c>
-      <c r="BV15" s="3" t="inlineStr">
+      <c r="BY15" s="3" t="inlineStr">
         <is>
           <t>HOME_PHONE</t>
         </is>
       </c>
-      <c r="BW15" s="3" t="inlineStr">
+      <c r="BZ15" s="3" t="inlineStr">
         <is>
           <t>7172343334</t>
         </is>
       </c>
-      <c r="BX15" s="3" t="inlineStr">
+      <c r="CA15" s="3" t="inlineStr">
         <is>
           <t>WORK_PHONE</t>
         </is>
       </c>
-      <c r="BY15" s="3" t="inlineStr">
+      <c r="CB15" s="3" t="inlineStr">
         <is>
           <t>7172341240</t>
         </is>
       </c>
-      <c r="BZ15"/>
-      <c r="CA15"/>
-      <c r="CB15"/>
       <c r="CC15"/>
       <c r="CD15"/>
       <c r="CE15"/>
@@ -11029,19 +11299,19 @@
       <c r="CZ15"/>
       <c r="DA15"/>
       <c r="DB15"/>
-      <c r="DC15" s="3" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="DD15" s="1" t="n">
-        <v>100.0</v>
-      </c>
+      <c r="DC15"/>
+      <c r="DD15"/>
       <c r="DE15"/>
       <c r="DF15"/>
       <c r="DG15"/>
-      <c r="DH15"/>
-      <c r="DI15"/>
+      <c r="DH15" s="3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="DI15" s="1" t="n">
+        <v>100.0</v>
+      </c>
       <c r="DJ15"/>
       <c r="DK15"/>
       <c r="DL15"/>
@@ -11349,11 +11619,22 @@
       <c r="PB15"/>
       <c r="PC15"/>
       <c r="PD15"/>
+      <c r="PE15"/>
+      <c r="PF15"/>
+      <c r="PG15"/>
+      <c r="PH15"/>
+      <c r="PI15"/>
+      <c r="PJ15"/>
+      <c r="PK15"/>
+      <c r="PL15"/>
+      <c r="PM15"/>
+      <c r="PN15"/>
+      <c r="PO15"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499ff14</t>
+          <t>6976904ee9a75feb6485522e</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -11443,28 +11724,28 @@
         </is>
       </c>
       <c r="AF16"/>
-      <c r="AG16" s="3" t="inlineStr">
+      <c r="AG16"/>
+      <c r="AH16"/>
+      <c r="AI16" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH16"/>
-      <c r="AI16"/>
       <c r="AJ16"/>
       <c r="AK16"/>
-      <c r="AL16" s="3" t="inlineStr">
+      <c r="AL16"/>
+      <c r="AM16"/>
+      <c r="AN16"/>
+      <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>202443307</t>
         </is>
       </c>
-      <c r="AM16" s="3" t="inlineStr">
+      <c r="AP16" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN16"/>
-      <c r="AO16"/>
-      <c r="AP16"/>
       <c r="AQ16"/>
       <c r="AR16"/>
       <c r="AS16"/>
@@ -11482,35 +11763,35 @@
       <c r="BE16"/>
       <c r="BF16"/>
       <c r="BG16"/>
-      <c r="BH16" s="3" t="inlineStr">
+      <c r="BH16"/>
+      <c r="BI16"/>
+      <c r="BJ16"/>
+      <c r="BK16" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI16" s="3" t="inlineStr">
+      <c r="BL16" s="3" t="inlineStr">
         <is>
           <t>MUTUALLY_DEFINED</t>
         </is>
       </c>
-      <c r="BJ16" s="3" t="inlineStr">
+      <c r="BM16" s="3" t="inlineStr">
         <is>
           <t>2024433307</t>
         </is>
       </c>
-      <c r="BK16"/>
-      <c r="BL16" s="3" t="inlineStr">
+      <c r="BN16"/>
+      <c r="BO16" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="BM16" s="3" t="inlineStr">
+      <c r="BP16" s="3" t="inlineStr">
         <is>
           <t>WILLIAM</t>
         </is>
       </c>
-      <c r="BN16"/>
-      <c r="BO16"/>
-      <c r="BP16"/>
       <c r="BQ16"/>
       <c r="BR16"/>
       <c r="BS16"/>
@@ -11705,32 +11986,32 @@
       <c r="IZ16"/>
       <c r="JA16"/>
       <c r="JB16"/>
-      <c r="JC16" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD16" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
+      <c r="JC16"/>
+      <c r="JD16"/>
       <c r="JE16"/>
       <c r="JF16"/>
       <c r="JG16"/>
       <c r="JH16" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI16" s="4" t="n">
-        <v>37438.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI16" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
       </c>
       <c r="JJ16"/>
       <c r="JK16"/>
       <c r="JL16"/>
-      <c r="JM16"/>
-      <c r="JN16"/>
+      <c r="JM16" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN16" s="4" t="n">
+        <v>37438.0</v>
+      </c>
       <c r="JO16"/>
       <c r="JP16"/>
       <c r="JQ16"/>
@@ -11877,11 +12158,22 @@
       <c r="PB16"/>
       <c r="PC16"/>
       <c r="PD16"/>
+      <c r="PE16"/>
+      <c r="PF16"/>
+      <c r="PG16"/>
+      <c r="PH16"/>
+      <c r="PI16"/>
+      <c r="PJ16"/>
+      <c r="PK16"/>
+      <c r="PL16"/>
+      <c r="PM16"/>
+      <c r="PN16"/>
+      <c r="PO16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499ff2c</t>
+          <t>6976904ee9a75feb64855246</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -11971,28 +12263,28 @@
         </is>
       </c>
       <c r="AF17"/>
-      <c r="AG17" s="3" t="inlineStr">
+      <c r="AG17"/>
+      <c r="AH17"/>
+      <c r="AI17" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH17"/>
-      <c r="AI17"/>
       <c r="AJ17"/>
       <c r="AK17"/>
-      <c r="AL17" s="3" t="inlineStr">
+      <c r="AL17"/>
+      <c r="AM17"/>
+      <c r="AN17"/>
+      <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
+      <c r="AP17" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN17"/>
-      <c r="AO17"/>
-      <c r="AP17"/>
       <c r="AQ17"/>
       <c r="AR17"/>
       <c r="AS17"/>
@@ -12000,56 +12292,56 @@
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
-      <c r="AX17" s="3" t="inlineStr">
+      <c r="AX17"/>
+      <c r="AY17"/>
+      <c r="AZ17"/>
+      <c r="BA17" s="3" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="AY17" s="4" t="n">
+      <c r="BB17" s="4" t="n">
         <v>35339.0</v>
       </c>
-      <c r="AZ17"/>
-      <c r="BA17"/>
-      <c r="BB17"/>
       <c r="BC17"/>
       <c r="BD17"/>
       <c r="BE17"/>
       <c r="BF17"/>
       <c r="BG17"/>
-      <c r="BH17" s="3" t="inlineStr">
+      <c r="BH17"/>
+      <c r="BI17"/>
+      <c r="BJ17"/>
+      <c r="BK17" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI17" s="3" t="inlineStr">
+      <c r="BL17" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ17" s="3" t="inlineStr">
+      <c r="BM17" s="3" t="inlineStr">
         <is>
           <t>103229876</t>
         </is>
       </c>
-      <c r="BK17"/>
-      <c r="BL17" s="3" t="inlineStr">
+      <c r="BN17"/>
+      <c r="BO17" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM17" s="3" t="inlineStr">
+      <c r="BP17" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="BN17" s="3" t="inlineStr">
+      <c r="BQ17" s="3" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="BO17"/>
-      <c r="BP17"/>
-      <c r="BQ17"/>
       <c r="BR17"/>
       <c r="BS17"/>
       <c r="BT17"/>
@@ -12401,11 +12693,22 @@
       <c r="PB17"/>
       <c r="PC17"/>
       <c r="PD17"/>
+      <c r="PE17"/>
+      <c r="PF17"/>
+      <c r="PG17"/>
+      <c r="PH17"/>
+      <c r="PI17"/>
+      <c r="PJ17"/>
+      <c r="PK17"/>
+      <c r="PL17"/>
+      <c r="PM17"/>
+      <c r="PN17"/>
+      <c r="PO17"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499ff48</t>
+          <t>6976904ee9a75feb64855262</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -12496,27 +12799,27 @@
       </c>
       <c r="AF18"/>
       <c r="AG18"/>
-      <c r="AH18" s="3" t="inlineStr">
+      <c r="AH18"/>
+      <c r="AI18"/>
+      <c r="AJ18" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AI18"/>
-      <c r="AJ18"/>
       <c r="AK18"/>
-      <c r="AL18" s="3" t="inlineStr">
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
+      <c r="AP18" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN18"/>
-      <c r="AO18"/>
-      <c r="AP18"/>
       <c r="AQ18"/>
       <c r="AR18"/>
       <c r="AS18"/>
@@ -12524,64 +12827,64 @@
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18"/>
-      <c r="AX18" s="3" t="inlineStr">
+      <c r="AX18"/>
+      <c r="AY18"/>
+      <c r="AZ18"/>
+      <c r="BA18" s="3" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="AY18" s="4" t="n">
+      <c r="BB18" s="4" t="n">
         <v>35930.0</v>
       </c>
-      <c r="AZ18"/>
-      <c r="BA18"/>
-      <c r="BB18"/>
       <c r="BC18"/>
       <c r="BD18"/>
       <c r="BE18"/>
       <c r="BF18"/>
       <c r="BG18"/>
-      <c r="BH18" s="3" t="inlineStr">
+      <c r="BH18"/>
+      <c r="BI18"/>
+      <c r="BJ18"/>
+      <c r="BK18" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI18" s="3" t="inlineStr">
+      <c r="BL18" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ18" s="3" t="inlineStr">
+      <c r="BM18" s="3" t="inlineStr">
         <is>
           <t>103229876</t>
         </is>
       </c>
-      <c r="BK18"/>
-      <c r="BL18" s="3" t="inlineStr">
+      <c r="BN18"/>
+      <c r="BO18" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM18" s="3" t="inlineStr">
+      <c r="BP18" s="3" t="inlineStr">
         <is>
           <t>JAMES</t>
         </is>
       </c>
-      <c r="BN18" s="3" t="inlineStr">
+      <c r="BQ18" s="3" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="BO18" s="4" t="n">
+      <c r="BR18" s="4" t="n">
         <v>28353.0</v>
       </c>
-      <c r="BP18" s="3" t="inlineStr">
+      <c r="BS18" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ18"/>
-      <c r="BR18"/>
-      <c r="BS18"/>
       <c r="BT18"/>
       <c r="BU18"/>
       <c r="BV18"/>
@@ -12659,16 +12962,16 @@
       <c r="EP18"/>
       <c r="EQ18"/>
       <c r="ER18"/>
-      <c r="ES18" s="3" t="inlineStr">
-        <is>
-          <t>PENN STATE UNIVERSITY</t>
-        </is>
-      </c>
+      <c r="ES18"/>
       <c r="ET18"/>
       <c r="EU18"/>
       <c r="EV18"/>
       <c r="EW18"/>
-      <c r="EX18"/>
+      <c r="EX18" s="3" t="inlineStr">
+        <is>
+          <t>PENN STATE UNIVERSITY</t>
+        </is>
+      </c>
       <c r="EY18"/>
       <c r="EZ18"/>
       <c r="FA18"/>
@@ -12777,32 +13080,32 @@
       <c r="IZ18"/>
       <c r="JA18"/>
       <c r="JB18"/>
-      <c r="JC18" s="3" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="JD18" s="3" t="inlineStr">
-        <is>
-          <t>HLT</t>
-        </is>
-      </c>
+      <c r="JC18"/>
+      <c r="JD18"/>
       <c r="JE18"/>
       <c r="JF18"/>
       <c r="JG18"/>
       <c r="JH18" s="3" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="JI18" s="4" t="n">
-        <v>35217.0</v>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="JI18" s="3" t="inlineStr">
+        <is>
+          <t>HLT</t>
+        </is>
       </c>
       <c r="JJ18"/>
       <c r="JK18"/>
       <c r="JL18"/>
-      <c r="JM18"/>
-      <c r="JN18"/>
+      <c r="JM18" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="JN18" s="4" t="n">
+        <v>35217.0</v>
+      </c>
       <c r="JO18"/>
       <c r="JP18"/>
       <c r="JQ18"/>
@@ -12949,11 +13252,22 @@
       <c r="PB18"/>
       <c r="PC18"/>
       <c r="PD18"/>
+      <c r="PE18"/>
+      <c r="PF18"/>
+      <c r="PG18"/>
+      <c r="PH18"/>
+      <c r="PI18"/>
+      <c r="PJ18"/>
+      <c r="PK18"/>
+      <c r="PL18"/>
+      <c r="PM18"/>
+      <c r="PN18"/>
+      <c r="PO18"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499ff61</t>
+          <t>6976904ee9a75feb6485527b</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13047,28 +13361,28 @@
         </is>
       </c>
       <c r="AF19"/>
-      <c r="AG19" s="3" t="inlineStr">
+      <c r="AG19"/>
+      <c r="AH19"/>
+      <c r="AI19" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="AH19"/>
-      <c r="AI19"/>
       <c r="AJ19"/>
       <c r="AK19"/>
-      <c r="AL19" s="3" t="inlineStr">
+      <c r="AL19"/>
+      <c r="AM19"/>
+      <c r="AN19"/>
+      <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
+      <c r="AP19" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN19"/>
-      <c r="AO19"/>
-      <c r="AP19"/>
       <c r="AQ19"/>
       <c r="AR19"/>
       <c r="AS19"/>
@@ -13086,48 +13400,48 @@
       <c r="BE19"/>
       <c r="BF19"/>
       <c r="BG19"/>
-      <c r="BH19" s="3" t="inlineStr">
+      <c r="BH19"/>
+      <c r="BI19"/>
+      <c r="BJ19"/>
+      <c r="BK19" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI19" s="3" t="inlineStr">
+      <c r="BL19" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ19" s="3" t="inlineStr">
+      <c r="BM19" s="3" t="inlineStr">
         <is>
           <t>103229876</t>
         </is>
       </c>
-      <c r="BK19"/>
-      <c r="BL19" s="3" t="inlineStr">
+      <c r="BN19"/>
+      <c r="BO19" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM19" s="3" t="inlineStr">
+      <c r="BP19" s="3" t="inlineStr">
         <is>
           <t>JAMES</t>
         </is>
       </c>
-      <c r="BN19" s="3" t="inlineStr">
+      <c r="BQ19" s="3" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="BO19" s="4" t="n">
+      <c r="BR19" s="4" t="n">
         <v>18368.0</v>
       </c>
-      <c r="BP19" s="3" t="inlineStr">
+      <c r="BS19" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ19"/>
-      <c r="BR19"/>
-      <c r="BS19"/>
       <c r="BT19"/>
       <c r="BU19"/>
       <c r="BV19"/>
@@ -13155,34 +13469,34 @@
       <c r="CR19"/>
       <c r="CS19"/>
       <c r="CT19"/>
-      <c r="CU19" s="3" t="inlineStr">
+      <c r="CU19"/>
+      <c r="CV19"/>
+      <c r="CW19"/>
+      <c r="CX19"/>
+      <c r="CY19"/>
+      <c r="CZ19" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="CV19" s="3" t="inlineStr">
+      <c r="DA19" s="3" t="inlineStr">
         <is>
           <t>JAMES</t>
         </is>
       </c>
-      <c r="CW19" s="3" t="inlineStr">
+      <c r="DB19" s="3" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="CX19" s="4" t="n">
+      <c r="DC19" s="4" t="n">
         <v>18369.0</v>
       </c>
-      <c r="CY19" s="3" t="inlineStr">
+      <c r="DD19" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="CZ19"/>
-      <c r="DA19"/>
-      <c r="DB19"/>
-      <c r="DC19"/>
-      <c r="DD19"/>
       <c r="DE19"/>
       <c r="DF19"/>
       <c r="DG19"/>
@@ -13495,11 +13809,22 @@
       <c r="PB19"/>
       <c r="PC19"/>
       <c r="PD19"/>
+      <c r="PE19"/>
+      <c r="PF19"/>
+      <c r="PG19"/>
+      <c r="PH19"/>
+      <c r="PI19"/>
+      <c r="PJ19"/>
+      <c r="PK19"/>
+      <c r="PL19"/>
+      <c r="PM19"/>
+      <c r="PN19"/>
+      <c r="PO19"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>690141ea7c0fb18b0499ff7a</t>
+          <t>6976904ee9a75feb64855294</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -13594,19 +13919,19 @@
       <c r="AI20"/>
       <c r="AJ20"/>
       <c r="AK20"/>
-      <c r="AL20" s="3" t="inlineStr">
+      <c r="AL20"/>
+      <c r="AM20"/>
+      <c r="AN20"/>
+      <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="AM20" s="3" t="inlineStr">
+      <c r="AP20" s="3" t="inlineStr">
         <is>
           <t>123456001</t>
         </is>
       </c>
-      <c r="AN20"/>
-      <c r="AO20"/>
-      <c r="AP20"/>
       <c r="AQ20"/>
       <c r="AR20"/>
       <c r="AS20"/>
@@ -13614,64 +13939,64 @@
       <c r="AU20"/>
       <c r="AV20"/>
       <c r="AW20"/>
-      <c r="AX20" s="3" t="inlineStr">
+      <c r="AX20"/>
+      <c r="AY20"/>
+      <c r="AZ20"/>
+      <c r="BA20" s="3" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="AY20" s="4" t="n">
+      <c r="BB20" s="4" t="n">
         <v>35278.0</v>
       </c>
-      <c r="AZ20"/>
-      <c r="BA20"/>
-      <c r="BB20"/>
       <c r="BC20"/>
       <c r="BD20"/>
       <c r="BE20"/>
       <c r="BF20"/>
       <c r="BG20"/>
-      <c r="BH20" s="3" t="inlineStr">
+      <c r="BH20"/>
+      <c r="BI20"/>
+      <c r="BJ20"/>
+      <c r="BK20" s="3" t="inlineStr">
         <is>
           <t>INSURED_SUBSCRIBER</t>
         </is>
       </c>
-      <c r="BI20" s="3" t="inlineStr">
+      <c r="BL20" s="3" t="inlineStr">
         <is>
           <t>SSN</t>
         </is>
       </c>
-      <c r="BJ20" s="3" t="inlineStr">
+      <c r="BM20" s="3" t="inlineStr">
         <is>
           <t>103229876</t>
         </is>
       </c>
-      <c r="BK20"/>
-      <c r="BL20" s="3" t="inlineStr">
+      <c r="BN20"/>
+      <c r="BO20" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="BM20" s="3" t="inlineStr">
+      <c r="BP20" s="3" t="inlineStr">
         <is>
           <t>JAMES</t>
         </is>
       </c>
-      <c r="BN20" s="3" t="inlineStr">
+      <c r="BQ20" s="3" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="BO20" s="4" t="n">
+      <c r="BR20" s="4" t="n">
         <v>28353.0</v>
       </c>
-      <c r="BP20" s="3" t="inlineStr">
+      <c r="BS20" s="3" t="inlineStr">
         <is>
           <t>MALE</t>
         </is>
       </c>
-      <c r="BQ20"/>
-      <c r="BR20"/>
-      <c r="BS20"/>
       <c r="BT20"/>
       <c r="BU20"/>
       <c r="BV20"/>
@@ -14021,6 +14346,17 @@
       <c r="PB20"/>
       <c r="PC20"/>
       <c r="PD20"/>
+      <c r="PE20"/>
+      <c r="PF20"/>
+      <c r="PG20"/>
+      <c r="PH20"/>
+      <c r="PI20"/>
+      <c r="PJ20"/>
+      <c r="PK20"/>
+      <c r="PL20"/>
+      <c r="PM20"/>
+      <c r="PN20"/>
+      <c r="PO20"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/converted_files/834/834-all-files.xlsx
+++ b/converted_files/834/834-all-files.xlsx
@@ -2222,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb648550cb</t>
+          <t>69e82c66836d7d05c9a0144d</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb648550e4</t>
+          <t>69e82c66836d7d05c9a01466</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb648550fb</t>
+          <t>69e82c66836d7d05c9a0147d</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855157</t>
+          <t>69e82c66836d7d05c9a014d9</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855158</t>
+          <t>69e82c66836d7d05c9a014da</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855159</t>
+          <t>69e82c66836d7d05c9a014db</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485515a</t>
+          <t>69e82c66836d7d05c9a014dc</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485517c</t>
+          <t>69e82c66836d7d05c9a014fe</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485517c</t>
+          <t>69e82c66836d7d05c9a014fe</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485517c</t>
+          <t>69e82c66836d7d05c9a014fe</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -8022,7 +8022,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855213</t>
+          <t>69e82c66836d7d05c9a01595</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="CQ12" s="3" t="inlineStr">
         <is>
-          <t>SalaryGrade</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="CR12" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="EF12" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EG12" s="3" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="EH12" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EI12" s="3" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="FD12" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FE12" s="3" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="FF12" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FG12" s="3" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="NO12" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="NP12" s="3" t="inlineStr">
@@ -9303,7 +9303,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855213</t>
+          <t>69e82c66836d7d05c9a01595</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="CQ13" s="3" t="inlineStr">
         <is>
-          <t>SalaryGrade</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="CR13" s="3" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="EF13" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EG13" s="3" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="EH13" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EI13" s="3" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="FD13" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FE13" s="3" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="FF13" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FG13" s="3" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855214</t>
+          <t>69e82c66836d7d05c9a01596</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855215</t>
+          <t>69e82c66836d7d05c9a01597</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -11072,7 +11072,7 @@
       <c r="M15"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>MasterPolicyNumbe2</t>
+          <t>MasterPolicyNumber2</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -11132,7 +11132,7 @@
       <c r="AG15"/>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK15" s="3" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485522e</t>
+          <t>69e82c66836d7d05c9a015b0</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855246</t>
+          <t>69e82c66836d7d05c9a015c8</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855262</t>
+          <t>69e82c66836d7d05c9a015e4</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -13267,7 +13267,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485527b</t>
+          <t>69e82c66836d7d05c9a015fd</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13824,7 +13824,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855294</t>
+          <t>69e82c66836d7d05c9a01616</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/converted_files/834/834-all-files.xlsx
+++ b/converted_files/834/834-all-files.xlsx
@@ -2222,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb648550cb</t>
+          <t>69efef03ad4799caa7f5a29a</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb648550e4</t>
+          <t>69efef03ad4799caa7f5a2b3</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb648550fb</t>
+          <t>69efef03ad4799caa7f5a2ca</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855157</t>
+          <t>69efef03ad4799caa7f5a326</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855158</t>
+          <t>69efef03ad4799caa7f5a327</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855159</t>
+          <t>69efef03ad4799caa7f5a328</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485515a</t>
+          <t>69efef03ad4799caa7f5a329</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485517c</t>
+          <t>69efef03ad4799caa7f5a34b</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485517c</t>
+          <t>69efef03ad4799caa7f5a34b</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485517c</t>
+          <t>69efef03ad4799caa7f5a34b</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -8022,7 +8022,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855213</t>
+          <t>69efef03ad4799caa7f5a3e2</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="CQ12" s="3" t="inlineStr">
         <is>
-          <t>SalaryGrade</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="CR12" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="EF12" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EG12" s="3" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="EH12" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EI12" s="3" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="FD12" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FE12" s="3" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="FF12" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FG12" s="3" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="NO12" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="NP12" s="3" t="inlineStr">
@@ -9303,7 +9303,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855213</t>
+          <t>69efef03ad4799caa7f5a3e2</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="CQ13" s="3" t="inlineStr">
         <is>
-          <t>SalaryGrade</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="CR13" s="3" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="EF13" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EG13" s="3" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="EH13" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="EI13" s="3" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="FD13" s="3" t="inlineStr">
         <is>
-          <t>HOME_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FE13" s="3" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="FF13" s="3" t="inlineStr">
         <is>
-          <t>WORK_PHONE</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="FG13" s="3" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855214</t>
+          <t>69efef03ad4799caa7f5a3e3</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855215</t>
+          <t>69efef03ad4799caa7f5a3e4</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -11072,7 +11072,7 @@
       <c r="M15"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>MasterPolicyNumbe2</t>
+          <t>MasterPolicyNumber2</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -11132,7 +11132,7 @@
       <c r="AG15"/>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK15" s="3" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485522e</t>
+          <t>69efef03ad4799caa7f5a3fd</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855246</t>
+          <t>69efef03ad4799caa7f5a415</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855262</t>
+          <t>69efef03ad4799caa7f5a431</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -13267,7 +13267,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb6485527b</t>
+          <t>69efef03ad4799caa7f5a44a</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13824,7 +13824,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6976904ee9a75feb64855294</t>
+          <t>69efef03ad4799caa7f5a463</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/converted_files/834/834-all-files.xlsx
+++ b/converted_files/834/834-all-files.xlsx
@@ -2222,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a0144d</t>
+          <t>6a04c9e730180e9da6b3f89e</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a01466</t>
+          <t>6a04c9e730180e9da6b3f8b7</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a0147d</t>
+          <t>6a04c9e730180e9da6b3f8ce</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a014d9</t>
+          <t>6a04c9e730180e9da6b3f92a</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a014da</t>
+          <t>6a04c9e730180e9da6b3f92b</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a014db</t>
+          <t>6a04c9e730180e9da6b3f92c</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a014dc</t>
+          <t>6a04c9e730180e9da6b3f92d</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a014fe</t>
+          <t>6a04c9e730180e9da6b3f94f</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a014fe</t>
+          <t>6a04c9e730180e9da6b3f94f</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a014fe</t>
+          <t>6a04c9e730180e9da6b3f94f</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -8022,7 +8022,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a01595</t>
+          <t>6a04c9e730180e9da6b3f9e6</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -9303,7 +9303,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a01595</t>
+          <t>6a04c9e730180e9da6b3f9e6</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a01596</t>
+          <t>6a04c9e730180e9da6b3f9e7</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a01597</t>
+          <t>6a04c9e730180e9da6b3f9e8</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a015b0</t>
+          <t>6a04c9e730180e9da6b3fa01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a015c8</t>
+          <t>6a04c9e730180e9da6b3fa19</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a015e4</t>
+          <t>6a04c9e730180e9da6b3fa35</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -13267,7 +13267,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a015fd</t>
+          <t>6a04c9e730180e9da6b3fa4e</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13824,7 +13824,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>69e82c66836d7d05c9a01616</t>
+          <t>6a04c9e730180e9da6b3fa67</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/converted_files/834/834-all-files.xlsx
+++ b/converted_files/834/834-all-files.xlsx
@@ -2222,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f89e</t>
+          <t>6a04cc581ef26d534baefed9</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f8b7</t>
+          <t>6a04cc581ef26d534baefef2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f8ce</t>
+          <t>6a04cc581ef26d534baeff09</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f92a</t>
+          <t>6a04cc581ef26d534baeff65</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f92b</t>
+          <t>6a04cc581ef26d534baeff66</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f92c</t>
+          <t>6a04cc581ef26d534baeff67</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f92d</t>
+          <t>6a04cc581ef26d534baeff68</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f94f</t>
+          <t>6a04cc581ef26d534baeff8a</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f94f</t>
+          <t>6a04cc581ef26d534baeff8a</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f94f</t>
+          <t>6a04cc581ef26d534baeff8a</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -8022,7 +8022,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f9e6</t>
+          <t>6a04cc581ef26d534baf0021</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -9303,7 +9303,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f9e6</t>
+          <t>6a04cc581ef26d534baf0021</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f9e7</t>
+          <t>6a04cc581ef26d534baf0022</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3f9e8</t>
+          <t>6a04cc581ef26d534baf0023</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3fa01</t>
+          <t>6a04cc581ef26d534baf003c</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3fa19</t>
+          <t>6a04cc581ef26d534baf0054</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3fa35</t>
+          <t>6a04cc581ef26d534baf0070</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -13267,7 +13267,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3fa4e</t>
+          <t>6a04cc591ef26d534baf0089</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13824,7 +13824,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a04c9e730180e9da6b3fa67</t>
+          <t>6a04cc591ef26d534baf00a2</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/converted_files/834/834-all-files.xlsx
+++ b/converted_files/834/834-all-files.xlsx
@@ -2222,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baefed9</t>
+          <t>6a32cb6197613a0e49905167</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baefef2</t>
+          <t>6a32cb6197613a0e49905182</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff09</t>
+          <t>6a32cb6197613a0e4990519b</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff65</t>
+          <t>6a32cb6197613a0e499051f9</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff66</t>
+          <t>6a32cb6197613a0e499051fa</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff67</t>
+          <t>6a32cb6197613a0e499051fb</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff68</t>
+          <t>6a32cb6197613a0e499051fc</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff8a</t>
+          <t>6a32cb6197613a0e49905220</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff8a</t>
+          <t>6a32cb6197613a0e49905220</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baeff8a</t>
+          <t>6a32cb6197613a0e49905220</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -8022,7 +8022,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baf0021</t>
+          <t>6a32cb6197613a0e499052b9</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -9303,7 +9303,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baf0021</t>
+          <t>6a32cb6197613a0e499052b9</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baf0022</t>
+          <t>6a32cb6197613a0e499052ba</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baf0023</t>
+          <t>6a32cb6197613a0e499052bb</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baf003c</t>
+          <t>6a32cb6197613a0e499052d6</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baf0054</t>
+          <t>6a32cb6197613a0e499052f0</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a04cc581ef26d534baf0070</t>
+          <t>6a32cb6197613a0e4990530e</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -13267,7 +13267,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0089</t>
+          <t>6a32cb6197613a0e49905329</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13824,7 +13824,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf00a2</t>
+          <t>6a32cb6197613a0e49905344</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/converted_files/834/834-all-files.xlsx
+++ b/converted_files/834/834-all-files.xlsx
@@ -2222,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e49905167</t>
+          <t>6a6914dfc22b0f540b824a35</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e49905182</t>
+          <t>6a6914e0c22b0f540b824a50</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e4990519b</t>
+          <t>6a6914e0c22b0f540b824a6a</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499051f9</t>
+          <t>6a6914e0c22b0f540b824a81</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499051fa</t>
+          <t>6a6914e0c22b0f540b824a93</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499051fb</t>
+          <t>6a6914e0c22b0f540b824aab</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499051fc</t>
+          <t>6a6914e0c22b0f540b824abd</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e49905220</t>
+          <t>6a6914e0c22b0f540b824ade</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e49905220</t>
+          <t>6a6914e0c22b0f540b824ade</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e49905220</t>
+          <t>6a6914e0c22b0f540b824ade</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -8022,7 +8022,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499052b9</t>
+          <t>6a6914e0c22b0f540b824b09</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -9303,7 +9303,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499052b9</t>
+          <t>6a6914e0c22b0f540b824b09</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499052ba</t>
+          <t>6a6914e0c22b0f540b824b62</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499052bb</t>
+          <t>6a6914e0c22b0f540b824b7b</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499052d6</t>
+          <t>6a6914e0c22b0f540b824b9a</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e499052f0</t>
+          <t>6a6914e0c22b0f540b824bb4</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e4990530e</t>
+          <t>6a6914e0c22b0f540b824bcd</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -13267,7 +13267,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e49905329</t>
+          <t>6a6914e0c22b0f540b824be9</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13824,7 +13824,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6197613a0e49905344</t>
+          <t>6a6914e0c22b0f540b824c04</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
